--- a/KBB Pricelist 2.xlsx
+++ b/KBB Pricelist 2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\Dropbox\Aztec shared\Quote related\current\5 - Costings\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayaan\Techmynt Solutions\aztec_interiors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AEB5B9-BAD6-4544-8426-FD184036DA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860D57B9-75E3-4849-9EBD-5FA0A7923BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1416" yWindow="444" windowWidth="20580" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kitchen" sheetId="1" r:id="rId1"/>
-    <sheet name="Bedroom" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Bedroom" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3158,36 +3161,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC336"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" style="6" customWidth="1"/>
-    <col min="8" max="12" width="11.5546875" style="6" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="6" customWidth="1"/>
+    <col min="8" max="12" width="11.5703125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D1" s="8">
         <v>2.2999999999999998</v>
       </c>
@@ -3204,7 +3207,7 @@
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
     </row>
-    <row r="2" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="110" t="s">
         <v>566</v>
       </c>
@@ -3223,7 +3226,7 @@
       <c r="AA2"/>
       <c r="AC2"/>
     </row>
-    <row r="3" spans="1:29" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="67" t="s">
         <v>59</v>
       </c>
@@ -3312,7 +3315,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
         <v>472</v>
       </c>
@@ -3337,7 +3340,10 @@
         <f>PRODUCT(E4,$G$1)</f>
         <v>21.450000000000003</v>
       </c>
-      <c r="H4" s="48"/>
+      <c r="H4" s="48">
+        <f>SUM(D4,G4)</f>
+        <v>90.45</v>
+      </c>
       <c r="I4" s="45"/>
       <c r="J4" s="49"/>
       <c r="K4" s="45"/>
@@ -3376,7 +3382,7 @@
       <c r="AB4" s="43"/>
       <c r="AC4" s="43"/>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>1</v>
       </c>
@@ -3401,7 +3407,10 @@
         <f t="shared" ref="G5:G13" si="2">PRODUCT(E5,$G$1)</f>
         <v>36.674999999999997</v>
       </c>
-      <c r="H5" s="19"/>
+      <c r="H5" s="48">
+        <f t="shared" ref="H5:H13" si="3">SUM(D5,G5)</f>
+        <v>115.10499999999999</v>
+      </c>
       <c r="I5" s="16"/>
       <c r="J5" s="20"/>
       <c r="K5" s="16"/>
@@ -3440,7 +3449,7 @@
       <c r="AB5" s="14"/>
       <c r="AC5" s="14"/>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>3</v>
       </c>
@@ -3465,7 +3474,10 @@
         <f t="shared" si="2"/>
         <v>43.664999999999999</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="48">
+        <f t="shared" si="3"/>
+        <v>124.625</v>
+      </c>
       <c r="I6" s="16"/>
       <c r="J6" s="20"/>
       <c r="K6" s="16"/>
@@ -3504,7 +3516,7 @@
       <c r="AB6" s="14"/>
       <c r="AC6" s="14"/>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>5</v>
       </c>
@@ -3529,7 +3541,10 @@
         <f t="shared" si="2"/>
         <v>46.980000000000004</v>
       </c>
-      <c r="H7" s="19"/>
+      <c r="H7" s="48">
+        <f t="shared" si="3"/>
+        <v>130.46999999999997</v>
+      </c>
       <c r="I7" s="16"/>
       <c r="J7" s="20"/>
       <c r="K7" s="16"/>
@@ -3568,7 +3583,7 @@
       <c r="AB7" s="14"/>
       <c r="AC7" s="14"/>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>7</v>
       </c>
@@ -3593,7 +3608,10 @@
         <f t="shared" si="2"/>
         <v>48.33</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="48">
+        <f t="shared" si="3"/>
+        <v>134.35</v>
+      </c>
       <c r="I8" s="16"/>
       <c r="J8" s="20"/>
       <c r="K8" s="16"/>
@@ -3632,7 +3650,7 @@
       <c r="AB8" s="14"/>
       <c r="AC8" s="14"/>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>9</v>
       </c>
@@ -3657,7 +3675,10 @@
         <f t="shared" si="2"/>
         <v>57.66</v>
       </c>
-      <c r="H9" s="19"/>
+      <c r="H9" s="48">
+        <f t="shared" si="3"/>
+        <v>146.20999999999998</v>
+      </c>
       <c r="I9" s="16"/>
       <c r="J9" s="20"/>
       <c r="K9" s="16"/>
@@ -3696,7 +3717,7 @@
       <c r="AB9" s="14"/>
       <c r="AC9" s="14"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>11</v>
       </c>
@@ -3721,7 +3742,10 @@
         <f t="shared" si="2"/>
         <v>87.33</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="48">
+        <f t="shared" si="3"/>
+        <v>186</v>
+      </c>
       <c r="I10" s="16"/>
       <c r="J10" s="20"/>
       <c r="K10" s="16"/>
@@ -3760,7 +3784,7 @@
       <c r="AB10" s="14"/>
       <c r="AC10" s="14"/>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>13</v>
       </c>
@@ -3785,7 +3809,10 @@
         <f t="shared" si="2"/>
         <v>93.960000000000008</v>
       </c>
-      <c r="H11" s="19"/>
+      <c r="H11" s="48">
+        <f t="shared" si="3"/>
+        <v>195.16</v>
+      </c>
       <c r="I11" s="16"/>
       <c r="J11" s="20"/>
       <c r="K11" s="16"/>
@@ -3824,7 +3851,7 @@
       <c r="AB11" s="14"/>
       <c r="AC11" s="14"/>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>15</v>
       </c>
@@ -3849,7 +3876,10 @@
         <f t="shared" si="2"/>
         <v>96.66</v>
       </c>
-      <c r="H12" s="19"/>
+      <c r="H12" s="48">
+        <f t="shared" si="3"/>
+        <v>200.39</v>
+      </c>
       <c r="I12" s="16"/>
       <c r="J12" s="20"/>
       <c r="K12" s="16"/>
@@ -3888,7 +3918,7 @@
       <c r="AB12" s="14"/>
       <c r="AC12" s="14"/>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>17</v>
       </c>
@@ -3913,7 +3943,10 @@
         <f t="shared" si="2"/>
         <v>115.32</v>
       </c>
-      <c r="H13" s="19"/>
+      <c r="H13" s="48">
+        <f t="shared" si="3"/>
+        <v>224.10999999999999</v>
+      </c>
       <c r="I13" s="16"/>
       <c r="J13" s="20"/>
       <c r="K13" s="16"/>
@@ -3952,7 +3985,7 @@
       <c r="AB13" s="14"/>
       <c r="AC13" s="14"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
       <c r="B14" s="25" t="s">
         <v>19</v>
@@ -3985,7 +4018,7 @@
       <c r="AB14" s="14"/>
       <c r="AC14" s="14"/>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="25" t="s">
         <v>20</v>
@@ -4024,7 +4057,7 @@
       <c r="AB15" s="14"/>
       <c r="AC15" s="14"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>21</v>
       </c>
@@ -4059,7 +4092,7 @@
       <c r="AB16" s="14"/>
       <c r="AC16" s="14"/>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="15"/>
       <c r="C17" s="54"/>
@@ -4090,7 +4123,7 @@
       <c r="AB17" s="14"/>
       <c r="AC17" s="14"/>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>23</v>
       </c>
@@ -4101,7 +4134,7 @@
         <v>55.1</v>
       </c>
       <c r="D18" s="16">
-        <f t="shared" ref="D18:D26" si="3">PRODUCT(C18,$D$1)</f>
+        <f t="shared" ref="D18:D26" si="4">PRODUCT(C18,$D$1)</f>
         <v>126.72999999999999</v>
       </c>
       <c r="E18" s="16">
@@ -4109,7 +4142,7 @@
       </c>
       <c r="F18" s="31"/>
       <c r="G18" s="16">
-        <f t="shared" ref="G18:G26" si="4">PRODUCT(E18,$G$1)</f>
+        <f t="shared" ref="G18:G26" si="5">PRODUCT(E18,$G$1)</f>
         <v>43.875</v>
       </c>
       <c r="H18" s="19"/>
@@ -4157,7 +4190,7 @@
       <c r="AB18" s="14"/>
       <c r="AC18" s="14"/>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>25</v>
       </c>
@@ -4168,7 +4201,7 @@
         <v>56.2</v>
       </c>
       <c r="D19" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>129.26</v>
       </c>
       <c r="E19" s="16">
@@ -4176,7 +4209,7 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>50.414999999999999</v>
       </c>
       <c r="H19" s="19"/>
@@ -4224,7 +4257,7 @@
       <c r="AB19" s="14"/>
       <c r="AC19" s="14"/>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>27</v>
       </c>
@@ -4235,7 +4268,7 @@
         <v>57.3</v>
       </c>
       <c r="D20" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>131.79</v>
       </c>
       <c r="E20" s="16">
@@ -4243,7 +4276,7 @@
       </c>
       <c r="F20" s="31"/>
       <c r="G20" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>54.39</v>
       </c>
       <c r="H20" s="19"/>
@@ -4291,7 +4324,7 @@
       <c r="AB20" s="14"/>
       <c r="AC20" s="14"/>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>29</v>
       </c>
@@ -4302,7 +4335,7 @@
         <v>58.4</v>
       </c>
       <c r="D21" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>134.32</v>
       </c>
       <c r="E21" s="16">
@@ -4310,7 +4343,7 @@
       </c>
       <c r="F21" s="31"/>
       <c r="G21" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>58.364999999999995</v>
       </c>
       <c r="H21" s="19"/>
@@ -4358,7 +4391,7 @@
       <c r="AB21" s="14"/>
       <c r="AC21" s="14"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>31</v>
       </c>
@@ -4369,7 +4402,7 @@
         <v>59.5</v>
       </c>
       <c r="D22" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>136.85</v>
       </c>
       <c r="E22" s="16">
@@ -4377,7 +4410,7 @@
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>65.429999999999993</v>
       </c>
       <c r="H22" s="19"/>
@@ -4425,7 +4458,7 @@
       <c r="AB22" s="14"/>
       <c r="AC22" s="14"/>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>33</v>
       </c>
@@ -4436,7 +4469,7 @@
         <v>74.900000000000006</v>
       </c>
       <c r="D23" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>172.27</v>
       </c>
       <c r="E23" s="16">
@@ -4444,7 +4477,7 @@
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>100.83</v>
       </c>
       <c r="H23" s="19"/>
@@ -4492,7 +4525,7 @@
       <c r="AB23" s="14"/>
       <c r="AC23" s="14"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>35</v>
       </c>
@@ -4503,7 +4536,7 @@
         <v>76</v>
       </c>
       <c r="D24" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>174.79999999999998</v>
       </c>
       <c r="E24" s="16">
@@ -4511,7 +4544,7 @@
       </c>
       <c r="F24" s="31"/>
       <c r="G24" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>108.78</v>
       </c>
       <c r="H24" s="19"/>
@@ -4559,7 +4592,7 @@
       <c r="AB24" s="14"/>
       <c r="AC24" s="14"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>37</v>
       </c>
@@ -4570,7 +4603,7 @@
         <v>77.099999999999994</v>
       </c>
       <c r="D25" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>177.32999999999998</v>
       </c>
       <c r="E25" s="16">
@@ -4578,7 +4611,7 @@
       </c>
       <c r="F25" s="31"/>
       <c r="G25" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>116.72999999999999</v>
       </c>
       <c r="H25" s="19"/>
@@ -4626,7 +4659,7 @@
       <c r="AB25" s="14"/>
       <c r="AC25" s="14"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>39</v>
       </c>
@@ -4637,7 +4670,7 @@
         <v>79.3</v>
       </c>
       <c r="D26" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>182.39</v>
       </c>
       <c r="E26" s="16">
@@ -4645,7 +4678,7 @@
       </c>
       <c r="F26" s="31"/>
       <c r="G26" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>130.85999999999999</v>
       </c>
       <c r="H26" s="19"/>
@@ -4693,7 +4726,7 @@
       <c r="AB26" s="14"/>
       <c r="AC26" s="14"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="25" t="s">
         <v>19</v>
@@ -4726,7 +4759,7 @@
       <c r="AB27" s="14"/>
       <c r="AC27" s="14"/>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="25" t="s">
         <v>586</v>
@@ -4759,7 +4792,7 @@
       <c r="AB28" s="14"/>
       <c r="AC28" s="14"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="25" t="s">
         <v>41</v>
@@ -4792,7 +4825,7 @@
       <c r="AB29" s="14"/>
       <c r="AC29" s="14"/>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="25" t="s">
         <v>42</v>
@@ -4825,7 +4858,7 @@
       <c r="AB30" s="14"/>
       <c r="AC30" s="14"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="15"/>
       <c r="C31" s="54"/>
@@ -4856,7 +4889,7 @@
       <c r="AB31" s="14"/>
       <c r="AC31" s="14"/>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
       <c r="B32" s="15"/>
       <c r="C32" s="54"/>
@@ -4887,7 +4920,7 @@
       <c r="AB32" s="14"/>
       <c r="AC32" s="14"/>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>43</v>
       </c>
@@ -4898,7 +4931,7 @@
         <v>48.4</v>
       </c>
       <c r="D33" s="16">
-        <f t="shared" ref="D33:D39" si="5">PRODUCT(C33,$D$1)</f>
+        <f t="shared" ref="D33:D39" si="6">PRODUCT(C33,$D$1)</f>
         <v>111.32</v>
       </c>
       <c r="E33" s="16">
@@ -4906,7 +4939,7 @@
       </c>
       <c r="F33" s="31"/>
       <c r="G33" s="16">
-        <f t="shared" ref="G33:G39" si="6">PRODUCT(E33,$G$1)</f>
+        <f t="shared" ref="G33:G39" si="7">PRODUCT(E33,$G$1)</f>
         <v>43.664999999999999</v>
       </c>
       <c r="H33" s="19"/>
@@ -4948,7 +4981,7 @@
       <c r="AB33" s="14"/>
       <c r="AC33" s="14"/>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>44</v>
       </c>
@@ -4959,7 +4992,7 @@
         <v>49.5</v>
       </c>
       <c r="D34" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>113.85</v>
       </c>
       <c r="E34" s="16">
@@ -4967,7 +5000,7 @@
       </c>
       <c r="F34" s="31"/>
       <c r="G34" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>46.980000000000004</v>
       </c>
       <c r="H34" s="19"/>
@@ -5009,7 +5042,7 @@
       <c r="AB34" s="14"/>
       <c r="AC34" s="14"/>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>45</v>
       </c>
@@ -5020,7 +5053,7 @@
         <v>50.6</v>
       </c>
       <c r="D35" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>116.38</v>
       </c>
       <c r="E35" s="16">
@@ -5028,7 +5061,7 @@
       </c>
       <c r="F35" s="31"/>
       <c r="G35" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>48.33</v>
       </c>
       <c r="H35" s="19"/>
@@ -5070,7 +5103,7 @@
       <c r="AB35" s="14"/>
       <c r="AC35" s="14"/>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>46</v>
       </c>
@@ -5081,7 +5114,7 @@
         <v>51.7</v>
       </c>
       <c r="D36" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>118.91</v>
       </c>
       <c r="E36" s="16">
@@ -5089,7 +5122,7 @@
       </c>
       <c r="F36" s="31"/>
       <c r="G36" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>57.66</v>
       </c>
       <c r="H36" s="19"/>
@@ -5131,7 +5164,7 @@
       <c r="AB36" s="14"/>
       <c r="AC36" s="14"/>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="14"/>
       <c r="B37" s="36" t="s">
         <v>591</v>
@@ -5140,7 +5173,7 @@
         <v>52.8</v>
       </c>
       <c r="D37" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>121.43999999999998</v>
       </c>
       <c r="E37" s="16">
@@ -5148,7 +5181,7 @@
       </c>
       <c r="F37" s="31"/>
       <c r="G37" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>57.66</v>
       </c>
       <c r="H37" s="19"/>
@@ -5174,7 +5207,7 @@
       <c r="AB37" s="14"/>
       <c r="AC37" s="14"/>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>467</v>
       </c>
@@ -5185,7 +5218,7 @@
         <v>50.6</v>
       </c>
       <c r="D38" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>116.38</v>
       </c>
       <c r="E38" s="16">
@@ -5193,7 +5226,7 @@
       </c>
       <c r="F38" s="31"/>
       <c r="G38" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>48.33</v>
       </c>
       <c r="H38" s="19"/>
@@ -5235,7 +5268,7 @@
       <c r="AB38" s="14"/>
       <c r="AC38" s="14"/>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>468</v>
       </c>
@@ -5246,7 +5279,7 @@
         <v>51.7</v>
       </c>
       <c r="D39" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>118.91</v>
       </c>
       <c r="E39" s="16">
@@ -5254,7 +5287,7 @@
       </c>
       <c r="F39" s="31"/>
       <c r="G39" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>57.66</v>
       </c>
       <c r="H39" s="19"/>
@@ -5296,7 +5329,7 @@
       <c r="AB39" s="14"/>
       <c r="AC39" s="14"/>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="14"/>
       <c r="B40" s="25" t="s">
         <v>19</v>
@@ -5329,7 +5362,7 @@
       <c r="AB40" s="14"/>
       <c r="AC40" s="14"/>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="14"/>
       <c r="B41" s="25" t="s">
         <v>20</v>
@@ -5362,7 +5395,7 @@
       <c r="AB41" s="14"/>
       <c r="AC41" s="14"/>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="14"/>
       <c r="B42" s="15"/>
       <c r="C42" s="54"/>
@@ -5393,7 +5426,7 @@
       <c r="AB42" s="14"/>
       <c r="AC42" s="14"/>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="14"/>
       <c r="B43" s="15"/>
       <c r="C43" s="54"/>
@@ -5424,7 +5457,7 @@
       <c r="AB43" s="14"/>
       <c r="AC43" s="14"/>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>47</v>
       </c>
@@ -5443,7 +5476,7 @@
       </c>
       <c r="F44" s="31"/>
       <c r="G44" s="16">
-        <f t="shared" ref="G44:G46" si="7">PRODUCT(E44,$G$1)</f>
+        <f t="shared" ref="G44:G46" si="8">PRODUCT(E44,$G$1)</f>
         <v>81.06</v>
       </c>
       <c r="H44" s="19"/>
@@ -5491,7 +5524,7 @@
       <c r="AB44" s="14"/>
       <c r="AC44" s="14"/>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>477</v>
       </c>
@@ -5502,7 +5535,7 @@
         <v>80.3</v>
       </c>
       <c r="D45" s="16">
-        <f t="shared" ref="D45:D46" si="8">PRODUCT(C45,$D$1)</f>
+        <f t="shared" ref="D45:D46" si="9">PRODUCT(C45,$D$1)</f>
         <v>184.68999999999997</v>
       </c>
       <c r="E45" s="16">
@@ -5510,7 +5543,7 @@
       </c>
       <c r="F45" s="31"/>
       <c r="G45" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>81.06</v>
       </c>
       <c r="H45" s="19"/>
@@ -5558,7 +5591,7 @@
       <c r="AB45" s="14"/>
       <c r="AC45" s="14"/>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>48</v>
       </c>
@@ -5569,7 +5602,7 @@
         <v>83.6</v>
       </c>
       <c r="D46" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>192.27999999999997</v>
       </c>
       <c r="E46" s="16">
@@ -5577,7 +5610,7 @@
       </c>
       <c r="F46" s="31"/>
       <c r="G46" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>48.33</v>
       </c>
       <c r="H46" s="19"/>
@@ -5619,7 +5652,7 @@
       <c r="AB46" s="14"/>
       <c r="AC46" s="14"/>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="14"/>
       <c r="B47" s="25" t="s">
         <v>19</v>
@@ -5652,7 +5685,7 @@
       <c r="AB47" s="14"/>
       <c r="AC47" s="14"/>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="14"/>
       <c r="B48" s="15"/>
       <c r="C48" s="54"/>
@@ -5683,7 +5716,7 @@
       <c r="AB48" s="14"/>
       <c r="AC48" s="14"/>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>49</v>
       </c>
@@ -5694,7 +5727,7 @@
         <v>40.700000000000003</v>
       </c>
       <c r="D49" s="16">
-        <f t="shared" ref="D49:D50" si="9">PRODUCT(C49,$D$1)</f>
+        <f t="shared" ref="D49:D50" si="10">PRODUCT(C49,$D$1)</f>
         <v>93.61</v>
       </c>
       <c r="E49" s="16">
@@ -5702,7 +5735,7 @@
       </c>
       <c r="F49" s="31"/>
       <c r="G49" s="16">
-        <f t="shared" ref="G49:G50" si="10">PRODUCT(E49,$G$1)</f>
+        <f t="shared" ref="G49:G50" si="11">PRODUCT(E49,$G$1)</f>
         <v>36.674999999999997</v>
       </c>
       <c r="H49" s="19"/>
@@ -5744,7 +5777,7 @@
       <c r="AB49" s="14"/>
       <c r="AC49" s="14"/>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>51</v>
       </c>
@@ -5755,7 +5788,7 @@
         <v>42.9</v>
       </c>
       <c r="D50" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>98.669999999999987</v>
       </c>
       <c r="E50" s="16">
@@ -5763,7 +5796,7 @@
       </c>
       <c r="F50" s="31"/>
       <c r="G50" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>43.664999999999999</v>
       </c>
       <c r="H50" s="19"/>
@@ -5805,7 +5838,7 @@
       <c r="AB50" s="14"/>
       <c r="AC50" s="14"/>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="14"/>
       <c r="B51" s="25" t="s">
         <v>19</v>
@@ -5838,7 +5871,7 @@
       <c r="AB51" s="14"/>
       <c r="AC51" s="14"/>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="14"/>
       <c r="B52" s="15"/>
       <c r="C52" s="54"/>
@@ -5869,7 +5902,7 @@
       <c r="AB52" s="14"/>
       <c r="AC52" s="14"/>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>53</v>
       </c>
@@ -5880,7 +5913,7 @@
         <v>39.6</v>
       </c>
       <c r="D53" s="16">
-        <f t="shared" ref="D53:D58" si="11">PRODUCT(C53,$D$1)</f>
+        <f t="shared" ref="D53:D58" si="12">PRODUCT(C53,$D$1)</f>
         <v>91.08</v>
       </c>
       <c r="E53" s="16">
@@ -5933,7 +5966,7 @@
       <c r="AB53" s="14"/>
       <c r="AC53" s="14"/>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>54</v>
       </c>
@@ -5944,7 +5977,7 @@
         <v>41.8</v>
       </c>
       <c r="D54" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>96.139999999999986</v>
       </c>
       <c r="E54" s="16">
@@ -5997,7 +6030,7 @@
       <c r="AB54" s="14"/>
       <c r="AC54" s="14"/>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>55</v>
       </c>
@@ -6008,7 +6041,7 @@
         <v>45.1</v>
       </c>
       <c r="D55" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>103.72999999999999</v>
       </c>
       <c r="E55" s="16">
@@ -6061,7 +6094,7 @@
       <c r="AB55" s="14"/>
       <c r="AC55" s="14"/>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>56</v>
       </c>
@@ -6072,7 +6105,7 @@
         <v>46.2</v>
       </c>
       <c r="D56" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>106.26</v>
       </c>
       <c r="E56" s="16">
@@ -6125,7 +6158,7 @@
       <c r="AB56" s="14"/>
       <c r="AC56" s="14"/>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>57</v>
       </c>
@@ -6136,7 +6169,7 @@
         <v>47.3</v>
       </c>
       <c r="D57" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>108.78999999999999</v>
       </c>
       <c r="E57" s="16">
@@ -6189,7 +6222,7 @@
       <c r="AB57" s="14"/>
       <c r="AC57" s="14"/>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>58</v>
       </c>
@@ -6200,7 +6233,7 @@
         <v>49.5</v>
       </c>
       <c r="D58" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>113.85</v>
       </c>
       <c r="E58" s="16">
@@ -6253,7 +6286,7 @@
       <c r="AB58" s="14"/>
       <c r="AC58" s="14"/>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
       <c r="B59" s="25" t="s">
         <v>19</v>
@@ -6286,7 +6319,7 @@
       <c r="AB59" s="14"/>
       <c r="AC59" s="14"/>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
       <c r="B60" s="25" t="s">
         <v>20</v>
@@ -6319,7 +6352,7 @@
       <c r="AB60" s="14"/>
       <c r="AC60" s="14"/>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
       <c r="B61" s="25"/>
       <c r="C61" s="76"/>
@@ -6350,7 +6383,7 @@
       <c r="AB61" s="14"/>
       <c r="AC61" s="14"/>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>60</v>
       </c>
@@ -6407,7 +6440,7 @@
       <c r="AB62" s="14"/>
       <c r="AC62" s="14"/>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>62</v>
       </c>
@@ -6464,7 +6497,7 @@
       <c r="AB63" s="14"/>
       <c r="AC63" s="14"/>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
       <c r="B64" s="109"/>
       <c r="C64" s="54"/>
@@ -6495,7 +6528,7 @@
       <c r="AB64" s="14"/>
       <c r="AC64" s="14"/>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
         <v>64</v>
       </c>
@@ -6506,7 +6539,7 @@
         <v>189</v>
       </c>
       <c r="D65" s="108">
-        <f t="shared" ref="D65:D69" si="12">PRODUCT(C65,$D$1)</f>
+        <f t="shared" ref="D65:D69" si="13">PRODUCT(C65,$D$1)</f>
         <v>434.7</v>
       </c>
       <c r="E65" s="16">
@@ -6553,7 +6586,7 @@
       <c r="AB65" s="14"/>
       <c r="AC65" s="14"/>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
         <v>65</v>
       </c>
@@ -6564,7 +6597,7 @@
         <v>190</v>
       </c>
       <c r="D66" s="108">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>436.99999999999994</v>
       </c>
       <c r="E66" s="16">
@@ -6611,7 +6644,7 @@
       <c r="AB66" s="14"/>
       <c r="AC66" s="14"/>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
         <v>67</v>
       </c>
@@ -6622,7 +6655,7 @@
         <v>191</v>
       </c>
       <c r="D67" s="108">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>439.29999999999995</v>
       </c>
       <c r="E67" s="16">
@@ -6669,7 +6702,7 @@
       <c r="AB67" s="14"/>
       <c r="AC67" s="14"/>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
         <v>69</v>
       </c>
@@ -6680,7 +6713,7 @@
         <v>192</v>
       </c>
       <c r="D68" s="108">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>441.59999999999997</v>
       </c>
       <c r="E68" s="16">
@@ -6727,7 +6760,7 @@
       <c r="AB68" s="14"/>
       <c r="AC68" s="14"/>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
         <v>71</v>
       </c>
@@ -6738,7 +6771,7 @@
         <v>193</v>
       </c>
       <c r="D69" s="108">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>443.9</v>
       </c>
       <c r="E69" s="16">
@@ -6785,7 +6818,7 @@
       <c r="AB69" s="14"/>
       <c r="AC69" s="14"/>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" s="14"/>
       <c r="B70" s="109"/>
       <c r="C70" s="54"/>
@@ -6816,7 +6849,7 @@
       <c r="AB70" s="14"/>
       <c r="AC70" s="14"/>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
         <v>73</v>
       </c>
@@ -6827,7 +6860,7 @@
         <v>139</v>
       </c>
       <c r="D71" s="108">
-        <f t="shared" ref="D71:D72" si="13">PRODUCT(C71,$D$1)</f>
+        <f t="shared" ref="D71:D72" si="14">PRODUCT(C71,$D$1)</f>
         <v>319.7</v>
       </c>
       <c r="E71" s="16">
@@ -6880,7 +6913,7 @@
       <c r="AB71" s="14"/>
       <c r="AC71" s="14"/>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
         <v>75</v>
       </c>
@@ -6891,7 +6924,7 @@
         <v>140</v>
       </c>
       <c r="D72" s="108">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>322</v>
       </c>
       <c r="E72" s="16">
@@ -6944,7 +6977,7 @@
       <c r="AB72" s="14"/>
       <c r="AC72" s="14"/>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" s="14"/>
       <c r="B73" s="109"/>
       <c r="C73" s="54"/>
@@ -6975,7 +7008,7 @@
       <c r="AB73" s="14"/>
       <c r="AC73" s="14"/>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
         <v>77</v>
       </c>
@@ -6986,7 +7019,7 @@
         <v>171</v>
       </c>
       <c r="D74" s="108">
-        <f t="shared" ref="D74:D75" si="14">PRODUCT(C74,$D$1)</f>
+        <f t="shared" ref="D74:D75" si="15">PRODUCT(C74,$D$1)</f>
         <v>393.29999999999995</v>
       </c>
       <c r="E74" s="16">
@@ -7039,7 +7072,7 @@
       <c r="AB74" s="14"/>
       <c r="AC74" s="14"/>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
         <v>79</v>
       </c>
@@ -7050,7 +7083,7 @@
         <v>172</v>
       </c>
       <c r="D75" s="108">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>395.59999999999997</v>
       </c>
       <c r="E75" s="16">
@@ -7103,7 +7136,7 @@
       <c r="AB75" s="14"/>
       <c r="AC75" s="14"/>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" s="14"/>
       <c r="B76" s="106"/>
       <c r="C76" s="54"/>
@@ -7134,7 +7167,7 @@
       <c r="AB76" s="14"/>
       <c r="AC76" s="14"/>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
         <v>81</v>
       </c>
@@ -7197,7 +7230,7 @@
       <c r="AB77" s="14"/>
       <c r="AC77" s="14"/>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
         <v>83</v>
       </c>
@@ -7260,7 +7293,7 @@
       <c r="AB78" s="14"/>
       <c r="AC78" s="14"/>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
         <v>85</v>
       </c>
@@ -7325,7 +7358,7 @@
       <c r="AB79" s="14"/>
       <c r="AC79" s="14"/>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
         <v>87</v>
       </c>
@@ -7388,7 +7421,7 @@
       <c r="AB80" s="14"/>
       <c r="AC80" s="14"/>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A81" s="14"/>
       <c r="B81" s="109"/>
       <c r="C81" s="54"/>
@@ -7419,7 +7452,7 @@
       <c r="AB81" s="14"/>
       <c r="AC81" s="14"/>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>89</v>
       </c>
@@ -7474,7 +7507,7 @@
       <c r="AB82" s="14"/>
       <c r="AC82" s="14"/>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
         <v>91</v>
       </c>
@@ -7529,7 +7562,7 @@
       <c r="AB83" s="14"/>
       <c r="AC83" s="14"/>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
         <v>93</v>
       </c>
@@ -7584,7 +7617,7 @@
       <c r="AB84" s="14"/>
       <c r="AC84" s="14"/>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A85" s="14" t="s">
         <v>95</v>
       </c>
@@ -7639,7 +7672,7 @@
       <c r="AB85" s="14"/>
       <c r="AC85" s="14"/>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" s="14" t="s">
         <v>97</v>
       </c>
@@ -7694,7 +7727,7 @@
       <c r="AB86" s="14"/>
       <c r="AC86" s="14"/>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87" s="14"/>
       <c r="B87" s="25" t="s">
         <v>19</v>
@@ -7727,7 +7760,7 @@
       <c r="AB87" s="14"/>
       <c r="AC87" s="14"/>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
       <c r="B88" s="25" t="s">
         <v>20</v>
@@ -7760,7 +7793,7 @@
       <c r="AB88" s="14"/>
       <c r="AC88" s="14"/>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" s="14"/>
       <c r="B89" s="25" t="s">
         <v>99</v>
@@ -7793,7 +7826,7 @@
       <c r="AB89" s="14"/>
       <c r="AC89" s="14"/>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" s="14"/>
       <c r="B90" s="15"/>
       <c r="C90" s="54"/>
@@ -7824,7 +7857,7 @@
       <c r="AB90" s="14"/>
       <c r="AC90" s="14"/>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
         <v>100</v>
       </c>
@@ -7882,7 +7915,7 @@
       <c r="AB91" s="14"/>
       <c r="AC91" s="14"/>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
         <v>102</v>
       </c>
@@ -7893,7 +7926,7 @@
         <v>44</v>
       </c>
       <c r="D92" s="108">
-        <f t="shared" ref="D92" si="15">PRODUCT(C92,$D$1)</f>
+        <f t="shared" ref="D92" si="16">PRODUCT(C92,$D$1)</f>
         <v>101.19999999999999</v>
       </c>
       <c r="E92" s="16"/>
@@ -7938,7 +7971,7 @@
       <c r="AB92" s="14"/>
       <c r="AC92" s="14"/>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" s="14"/>
       <c r="B93" s="109"/>
       <c r="C93" s="107"/>
@@ -7969,7 +8002,7 @@
       <c r="AB93" s="14"/>
       <c r="AC93" s="14"/>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
         <v>104</v>
       </c>
@@ -7980,7 +8013,7 @@
         <v>50.6</v>
       </c>
       <c r="D94" s="108">
-        <f t="shared" ref="D94:D95" si="16">PRODUCT(C94,$D$1)</f>
+        <f t="shared" ref="D94:D95" si="17">PRODUCT(C94,$D$1)</f>
         <v>116.38</v>
       </c>
       <c r="E94" s="16"/>
@@ -8025,7 +8058,7 @@
       <c r="AB94" s="14"/>
       <c r="AC94" s="14"/>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="14" t="s">
         <v>106</v>
       </c>
@@ -8036,7 +8069,7 @@
         <v>57.2</v>
       </c>
       <c r="D95" s="108">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>131.56</v>
       </c>
       <c r="E95" s="16"/>
@@ -8081,7 +8114,7 @@
       <c r="AB95" s="14"/>
       <c r="AC95" s="14"/>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" s="14"/>
       <c r="B96" s="109"/>
       <c r="C96" s="107"/>
@@ -8112,7 +8145,7 @@
       <c r="AB96" s="14"/>
       <c r="AC96" s="14"/>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
         <v>108</v>
       </c>
@@ -8168,7 +8201,7 @@
       <c r="AB97" s="14"/>
       <c r="AC97" s="14"/>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" s="14"/>
       <c r="B98" s="109"/>
       <c r="C98" s="107"/>
@@ -8199,7 +8232,7 @@
       <c r="AB98" s="14"/>
       <c r="AC98" s="14"/>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
         <v>108</v>
       </c>
@@ -8255,7 +8288,7 @@
       <c r="AB99" s="14"/>
       <c r="AC99" s="14"/>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100" s="14"/>
       <c r="B100" s="25" t="s">
         <v>111</v>
@@ -8288,7 +8321,7 @@
       <c r="AB100" s="14"/>
       <c r="AC100" s="14"/>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A101" s="14"/>
       <c r="B101" s="15"/>
       <c r="C101" s="54"/>
@@ -8319,7 +8352,7 @@
       <c r="AB101" s="14"/>
       <c r="AC101" s="14"/>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" s="14"/>
       <c r="B102" s="15"/>
       <c r="C102" s="54"/>
@@ -8350,7 +8383,7 @@
       <c r="AB102" s="14"/>
       <c r="AC102" s="14"/>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
         <v>112</v>
       </c>
@@ -8361,7 +8394,7 @@
         <v>80.3</v>
       </c>
       <c r="D103" s="16">
-        <f t="shared" ref="D103:D105" si="17">PRODUCT(C103,$D$1)</f>
+        <f t="shared" ref="D103:D105" si="18">PRODUCT(C103,$D$1)</f>
         <v>184.68999999999997</v>
       </c>
       <c r="E103" s="16"/>
@@ -8418,7 +8451,7 @@
       <c r="AB103" s="14"/>
       <c r="AC103" s="14"/>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
         <v>114</v>
       </c>
@@ -8429,7 +8462,7 @@
         <v>80.3</v>
       </c>
       <c r="D104" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>184.68999999999997</v>
       </c>
       <c r="E104" s="16"/>
@@ -8486,7 +8519,7 @@
       <c r="AB104" s="14"/>
       <c r="AC104" s="14"/>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
         <v>116</v>
       </c>
@@ -8497,7 +8530,7 @@
         <v>83.6</v>
       </c>
       <c r="D105" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>192.27999999999997</v>
       </c>
       <c r="E105" s="16"/>
@@ -8554,7 +8587,7 @@
       <c r="AB105" s="14"/>
       <c r="AC105" s="14"/>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A106" s="14"/>
       <c r="B106" s="15"/>
       <c r="C106" s="54"/>
@@ -8585,7 +8618,7 @@
       <c r="AB106" s="14"/>
       <c r="AC106" s="14"/>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
         <v>118</v>
       </c>
@@ -8596,7 +8629,7 @@
         <v>83.6</v>
       </c>
       <c r="D107" s="16">
-        <f t="shared" ref="D107:D109" si="18">PRODUCT(C107,$D$1)</f>
+        <f t="shared" ref="D107:D109" si="19">PRODUCT(C107,$D$1)</f>
         <v>192.27999999999997</v>
       </c>
       <c r="E107" s="16"/>
@@ -8653,7 +8686,7 @@
       <c r="AB107" s="14"/>
       <c r="AC107" s="14"/>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
         <v>120</v>
       </c>
@@ -8664,7 +8697,7 @@
         <v>83.6</v>
       </c>
       <c r="D108" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>192.27999999999997</v>
       </c>
       <c r="E108" s="16"/>
@@ -8721,7 +8754,7 @@
       <c r="AB108" s="14"/>
       <c r="AC108" s="14"/>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
         <v>122</v>
       </c>
@@ -8732,7 +8765,7 @@
         <v>84.6</v>
       </c>
       <c r="D109" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>194.57999999999998</v>
       </c>
       <c r="E109" s="16"/>
@@ -8789,7 +8822,7 @@
       <c r="AB109" s="14"/>
       <c r="AC109" s="14"/>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A110" s="14"/>
       <c r="B110" s="15"/>
       <c r="C110" s="54"/>
@@ -8820,7 +8853,7 @@
       <c r="AB110" s="14"/>
       <c r="AC110" s="14"/>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
         <v>473</v>
       </c>
@@ -8831,7 +8864,7 @@
         <v>160</v>
       </c>
       <c r="D111" s="16">
-        <f t="shared" ref="D111:D113" si="19">PRODUCT(C111,$D$1)</f>
+        <f t="shared" ref="D111:D113" si="20">PRODUCT(C111,$D$1)</f>
         <v>368</v>
       </c>
       <c r="E111" s="16"/>
@@ -8888,7 +8921,7 @@
       <c r="AB111" s="14"/>
       <c r="AC111" s="14"/>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
         <v>440</v>
       </c>
@@ -8899,7 +8932,7 @@
         <v>150</v>
       </c>
       <c r="D112" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>345</v>
       </c>
       <c r="E112" s="16"/>
@@ -8962,7 +8995,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
         <v>441</v>
       </c>
@@ -8973,7 +9006,7 @@
         <v>153</v>
       </c>
       <c r="D113" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>351.9</v>
       </c>
       <c r="E113" s="16"/>
@@ -9036,7 +9069,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A114" s="14"/>
       <c r="B114" s="15"/>
       <c r="C114" s="54"/>
@@ -9067,7 +9100,7 @@
       <c r="AB114" s="14"/>
       <c r="AC114" s="14"/>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
         <v>474</v>
       </c>
@@ -9078,7 +9111,7 @@
         <v>153.6</v>
       </c>
       <c r="D115" s="16">
-        <f t="shared" ref="D115:D117" si="20">PRODUCT(C115,$D$1)</f>
+        <f t="shared" ref="D115:D117" si="21">PRODUCT(C115,$D$1)</f>
         <v>353.28</v>
       </c>
       <c r="E115" s="16"/>
@@ -9135,7 +9168,7 @@
       <c r="AB115" s="14"/>
       <c r="AC115" s="14"/>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
         <v>442</v>
       </c>
@@ -9146,7 +9179,7 @@
         <v>153.6</v>
       </c>
       <c r="D116" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>353.28</v>
       </c>
       <c r="E116" s="16"/>
@@ -9209,7 +9242,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
         <v>443</v>
       </c>
@@ -9220,7 +9253,7 @@
         <v>154.6</v>
       </c>
       <c r="D117" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>355.58</v>
       </c>
       <c r="E117" s="16"/>
@@ -9283,7 +9316,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="14"/>
       <c r="B118" s="15"/>
       <c r="C118" s="54"/>
@@ -9314,7 +9347,7 @@
       <c r="AB118" s="14"/>
       <c r="AC118" s="14"/>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
         <v>124</v>
       </c>
@@ -9325,7 +9358,7 @@
         <v>79.2</v>
       </c>
       <c r="D119" s="16">
-        <f t="shared" ref="D119:D120" si="21">PRODUCT(C119,$D$1)</f>
+        <f t="shared" ref="D119:D120" si="22">PRODUCT(C119,$D$1)</f>
         <v>182.16</v>
       </c>
       <c r="E119" s="16"/>
@@ -9376,7 +9409,7 @@
       <c r="AB119" s="14"/>
       <c r="AC119" s="14"/>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
         <v>126</v>
       </c>
@@ -9387,7 +9420,7 @@
         <v>81.400000000000006</v>
       </c>
       <c r="D120" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>187.22</v>
       </c>
       <c r="E120" s="16"/>
@@ -9438,7 +9471,7 @@
       <c r="AB120" s="14"/>
       <c r="AC120" s="14"/>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="14"/>
       <c r="B121" s="15"/>
       <c r="C121" s="76"/>
@@ -9469,7 +9502,7 @@
       <c r="AB121" s="14"/>
       <c r="AC121" s="14"/>
     </row>
-    <row r="122" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="78" t="s">
         <v>59</v>
       </c>
@@ -9540,7 +9573,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A123" s="14"/>
       <c r="B123" s="15"/>
       <c r="C123" s="54"/>
@@ -9571,7 +9604,7 @@
       <c r="AB123" s="14"/>
       <c r="AC123" s="14"/>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
         <v>446</v>
       </c>
@@ -9582,7 +9615,7 @@
         <v>80.3</v>
       </c>
       <c r="D124" s="16">
-        <f t="shared" ref="D124:D128" si="22">PRODUCT(C124,$D$1)</f>
+        <f t="shared" ref="D124:D128" si="23">PRODUCT(C124,$D$1)</f>
         <v>184.68999999999997</v>
       </c>
       <c r="E124" s="16"/>
@@ -9633,7 +9666,7 @@
       <c r="AB124" s="14"/>
       <c r="AC124" s="14"/>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
         <v>447</v>
       </c>
@@ -9644,7 +9677,7 @@
         <v>81.400000000000006</v>
       </c>
       <c r="D125" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>187.22</v>
       </c>
       <c r="E125" s="16"/>
@@ -9695,7 +9728,7 @@
       <c r="AB125" s="14"/>
       <c r="AC125" s="14"/>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
         <v>448</v>
       </c>
@@ -9706,7 +9739,7 @@
         <v>82.5</v>
       </c>
       <c r="D126" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>189.74999999999997</v>
       </c>
       <c r="E126" s="16"/>
@@ -9757,7 +9790,7 @@
       <c r="AB126" s="14"/>
       <c r="AC126" s="14"/>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
         <v>449</v>
       </c>
@@ -9768,7 +9801,7 @@
         <v>83.6</v>
       </c>
       <c r="D127" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>192.27999999999997</v>
       </c>
       <c r="E127" s="16"/>
@@ -9819,7 +9852,7 @@
       <c r="AB127" s="14"/>
       <c r="AC127" s="14"/>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A128" s="14" t="s">
         <v>450</v>
       </c>
@@ -9830,7 +9863,7 @@
         <v>84.7</v>
       </c>
       <c r="D128" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>194.81</v>
       </c>
       <c r="E128" s="16"/>
@@ -9881,7 +9914,7 @@
       <c r="AB128" s="14"/>
       <c r="AC128" s="14"/>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A129" s="14"/>
       <c r="B129" s="15"/>
       <c r="C129" s="54"/>
@@ -9912,7 +9945,7 @@
       <c r="AB129" s="14"/>
       <c r="AC129" s="14"/>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A130" s="14" t="s">
         <v>451</v>
       </c>
@@ -9923,7 +9956,7 @@
         <v>83.6</v>
       </c>
       <c r="D130" s="16">
-        <f t="shared" ref="D130:D134" si="23">PRODUCT(C130,$D$1)</f>
+        <f t="shared" ref="D130:D134" si="24">PRODUCT(C130,$D$1)</f>
         <v>192.27999999999997</v>
       </c>
       <c r="E130" s="16"/>
@@ -9974,7 +10007,7 @@
       <c r="AB130" s="14"/>
       <c r="AC130" s="14"/>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A131" s="14" t="s">
         <v>452</v>
       </c>
@@ -9985,7 +10018,7 @@
         <v>84.7</v>
       </c>
       <c r="D131" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>194.81</v>
       </c>
       <c r="E131" s="16"/>
@@ -10036,7 +10069,7 @@
       <c r="AB131" s="14"/>
       <c r="AC131" s="14"/>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A132" s="14" t="s">
         <v>453</v>
       </c>
@@ -10047,7 +10080,7 @@
         <v>85.8</v>
       </c>
       <c r="D132" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>197.33999999999997</v>
       </c>
       <c r="E132" s="16"/>
@@ -10098,7 +10131,7 @@
       <c r="AB132" s="14"/>
       <c r="AC132" s="14"/>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="s">
         <v>454</v>
       </c>
@@ -10109,7 +10142,7 @@
         <v>86.9</v>
       </c>
       <c r="D133" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>199.87</v>
       </c>
       <c r="E133" s="16"/>
@@ -10160,7 +10193,7 @@
       <c r="AB133" s="14"/>
       <c r="AC133" s="14"/>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
         <v>455</v>
       </c>
@@ -10171,7 +10204,7 @@
         <v>88</v>
       </c>
       <c r="D134" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>202.39999999999998</v>
       </c>
       <c r="E134" s="16"/>
@@ -10222,7 +10255,7 @@
       <c r="AB134" s="14"/>
       <c r="AC134" s="14"/>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A135" s="14"/>
       <c r="B135" s="15"/>
       <c r="C135" s="54"/>
@@ -10253,7 +10286,7 @@
       <c r="AB135" s="14"/>
       <c r="AC135" s="14"/>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A136" s="14" t="s">
         <v>478</v>
       </c>
@@ -10264,7 +10297,7 @@
         <v>81.400000000000006</v>
       </c>
       <c r="D136" s="16">
-        <f t="shared" ref="D136:D137" si="24">PRODUCT(C136,$D$1)</f>
+        <f t="shared" ref="D136:D137" si="25">PRODUCT(C136,$D$1)</f>
         <v>187.22</v>
       </c>
       <c r="E136" s="16"/>
@@ -10315,7 +10348,7 @@
       <c r="AB136" s="14"/>
       <c r="AC136" s="14"/>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A137" s="14" t="s">
         <v>479</v>
       </c>
@@ -10326,7 +10359,7 @@
         <v>84.7</v>
       </c>
       <c r="D137" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>194.81</v>
       </c>
       <c r="E137" s="16"/>
@@ -10377,7 +10410,7 @@
       <c r="AB137" s="14"/>
       <c r="AC137" s="14"/>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A138" s="14"/>
       <c r="B138" s="15"/>
       <c r="C138" s="54"/>
@@ -10408,7 +10441,7 @@
       <c r="AB138" s="14"/>
       <c r="AC138" s="14"/>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A139" s="14" t="s">
         <v>533</v>
       </c>
@@ -10419,7 +10452,7 @@
         <v>83.6</v>
       </c>
       <c r="D139" s="16">
-        <f t="shared" ref="D139:D140" si="25">PRODUCT(C139,$D$1)</f>
+        <f t="shared" ref="D139:D140" si="26">PRODUCT(C139,$D$1)</f>
         <v>192.27999999999997</v>
       </c>
       <c r="E139" s="16"/>
@@ -10482,7 +10515,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A140" s="14" t="s">
         <v>534</v>
       </c>
@@ -10493,7 +10526,7 @@
         <v>84.7</v>
       </c>
       <c r="D140" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>194.81</v>
       </c>
       <c r="E140" s="16"/>
@@ -10556,7 +10589,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A141" s="14"/>
       <c r="B141" s="15"/>
       <c r="C141" s="54"/>
@@ -10587,7 +10620,7 @@
       <c r="AB141" s="14"/>
       <c r="AC141" s="14"/>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A142" s="14" t="s">
         <v>539</v>
       </c>
@@ -10598,7 +10631,7 @@
         <v>81.400000000000006</v>
       </c>
       <c r="D142" s="16">
-        <f t="shared" ref="D142:D143" si="26">PRODUCT(C142,$D$1)</f>
+        <f t="shared" ref="D142:D143" si="27">PRODUCT(C142,$D$1)</f>
         <v>187.22</v>
       </c>
       <c r="E142" s="16">
@@ -10651,7 +10684,7 @@
       <c r="AB142" s="14"/>
       <c r="AC142" s="14"/>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A143" s="14" t="s">
         <v>540</v>
       </c>
@@ -10662,7 +10695,7 @@
         <v>84.7</v>
       </c>
       <c r="D143" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>194.81</v>
       </c>
       <c r="E143" s="16">
@@ -10715,7 +10748,7 @@
       <c r="AB143" s="14"/>
       <c r="AC143" s="14"/>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A144" s="14"/>
       <c r="B144" s="15"/>
       <c r="C144" s="54"/>
@@ -10746,7 +10779,7 @@
       <c r="AB144" s="14"/>
       <c r="AC144" s="14"/>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A145" s="14" t="s">
         <v>138</v>
       </c>
@@ -10757,7 +10790,7 @@
         <v>25.3</v>
       </c>
       <c r="D145" s="16">
-        <f t="shared" ref="D145:D153" si="27">PRODUCT(C145,$D$1)</f>
+        <f t="shared" ref="D145:D153" si="28">PRODUCT(C145,$D$1)</f>
         <v>58.19</v>
       </c>
       <c r="E145" s="16">
@@ -10804,7 +10837,7 @@
       <c r="AB145" s="14"/>
       <c r="AC145" s="14"/>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A146" s="14" t="s">
         <v>140</v>
       </c>
@@ -10815,7 +10848,7 @@
         <v>26.4</v>
       </c>
       <c r="D146" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>60.719999999999992</v>
       </c>
       <c r="E146" s="16">
@@ -10862,7 +10895,7 @@
       <c r="AB146" s="14"/>
       <c r="AC146" s="14"/>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A147" s="14" t="s">
         <v>142</v>
       </c>
@@ -10873,7 +10906,7 @@
         <v>27.5</v>
       </c>
       <c r="D147" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>63.249999999999993</v>
       </c>
       <c r="E147" s="16">
@@ -10920,7 +10953,7 @@
       <c r="AB147" s="14"/>
       <c r="AC147" s="14"/>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A148" s="14" t="s">
         <v>144</v>
       </c>
@@ -10931,7 +10964,7 @@
         <v>28.6</v>
       </c>
       <c r="D148" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>65.78</v>
       </c>
       <c r="E148" s="16">
@@ -10978,7 +11011,7 @@
       <c r="AB148" s="14"/>
       <c r="AC148" s="14"/>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A149" s="14" t="s">
         <v>146</v>
       </c>
@@ -10989,7 +11022,7 @@
         <v>29.7</v>
       </c>
       <c r="D149" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>68.309999999999988</v>
       </c>
       <c r="E149" s="16">
@@ -11036,7 +11069,7 @@
       <c r="AB149" s="14"/>
       <c r="AC149" s="14"/>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A150" s="14" t="s">
         <v>148</v>
       </c>
@@ -11047,7 +11080,7 @@
         <v>33</v>
       </c>
       <c r="D150" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>75.899999999999991</v>
       </c>
       <c r="E150" s="16">
@@ -11094,7 +11127,7 @@
       <c r="AB150" s="14"/>
       <c r="AC150" s="14"/>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A151" s="14" t="s">
         <v>552</v>
       </c>
@@ -11105,7 +11138,7 @@
         <v>34</v>
       </c>
       <c r="D151" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>78.199999999999989</v>
       </c>
       <c r="E151" s="16">
@@ -11152,7 +11185,7 @@
       <c r="AB151" s="14"/>
       <c r="AC151" s="14"/>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A152" s="14" t="s">
         <v>150</v>
       </c>
@@ -11163,7 +11196,7 @@
         <v>35.200000000000003</v>
       </c>
       <c r="D152" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>80.959999999999994</v>
       </c>
       <c r="E152" s="16">
@@ -11210,7 +11243,7 @@
       <c r="AB152" s="14"/>
       <c r="AC152" s="14"/>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A153" s="14" t="s">
         <v>152</v>
       </c>
@@ -11221,7 +11254,7 @@
         <v>37.4</v>
       </c>
       <c r="D153" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>86.02</v>
       </c>
       <c r="E153" s="16"/>
@@ -11266,7 +11299,7 @@
       <c r="AB153" s="14"/>
       <c r="AC153" s="14"/>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A154" s="14"/>
       <c r="B154" s="25" t="s">
         <v>154</v>
@@ -11299,7 +11332,7 @@
       <c r="AB154" s="14"/>
       <c r="AC154" s="14"/>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A155" s="14"/>
       <c r="B155" s="15"/>
       <c r="C155" s="54"/>
@@ -11330,7 +11363,7 @@
       <c r="AB155" s="14"/>
       <c r="AC155" s="14"/>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A156" s="14"/>
       <c r="B156" s="15"/>
       <c r="C156" s="54"/>
@@ -11361,7 +11394,7 @@
       <c r="AB156" s="14"/>
       <c r="AC156" s="14"/>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A157" s="14" t="s">
         <v>155</v>
       </c>
@@ -11372,7 +11405,7 @@
         <v>26.4</v>
       </c>
       <c r="D157" s="16">
-        <f t="shared" ref="D157:D165" si="28">PRODUCT(C157,$D$1)</f>
+        <f t="shared" ref="D157:D165" si="29">PRODUCT(C157,$D$1)</f>
         <v>60.719999999999992</v>
       </c>
       <c r="E157" s="16">
@@ -11419,7 +11452,7 @@
       <c r="AB157" s="14"/>
       <c r="AC157" s="14"/>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A158" s="14" t="s">
         <v>157</v>
       </c>
@@ -11430,7 +11463,7 @@
         <v>27.5</v>
       </c>
       <c r="D158" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>63.249999999999993</v>
       </c>
       <c r="E158" s="16">
@@ -11477,7 +11510,7 @@
       <c r="AB158" s="14"/>
       <c r="AC158" s="14"/>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A159" s="14" t="s">
         <v>159</v>
       </c>
@@ -11488,7 +11521,7 @@
         <v>28.6</v>
       </c>
       <c r="D159" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>65.78</v>
       </c>
       <c r="E159" s="16">
@@ -11535,7 +11568,7 @@
       <c r="AB159" s="14"/>
       <c r="AC159" s="14"/>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
         <v>161</v>
       </c>
@@ -11546,7 +11579,7 @@
         <v>29.7</v>
       </c>
       <c r="D160" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>68.309999999999988</v>
       </c>
       <c r="E160" s="16">
@@ -11593,7 +11626,7 @@
       <c r="AB160" s="14"/>
       <c r="AC160" s="14"/>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
         <v>163</v>
       </c>
@@ -11604,7 +11637,7 @@
         <v>30.8</v>
       </c>
       <c r="D161" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>70.839999999999989</v>
       </c>
       <c r="E161" s="16">
@@ -11651,7 +11684,7 @@
       <c r="AB161" s="14"/>
       <c r="AC161" s="14"/>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A162" s="14" t="s">
         <v>165</v>
       </c>
@@ -11662,7 +11695,7 @@
         <v>35.200000000000003</v>
       </c>
       <c r="D162" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>80.959999999999994</v>
       </c>
       <c r="E162" s="16">
@@ -11709,7 +11742,7 @@
       <c r="AB162" s="14"/>
       <c r="AC162" s="14"/>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A163" s="14" t="s">
         <v>550</v>
       </c>
@@ -11720,7 +11753,7 @@
         <v>36.200000000000003</v>
       </c>
       <c r="D163" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>83.26</v>
       </c>
       <c r="E163" s="16">
@@ -11767,7 +11800,7 @@
       <c r="AB163" s="14"/>
       <c r="AC163" s="14"/>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A164" s="14" t="s">
         <v>167</v>
       </c>
@@ -11778,7 +11811,7 @@
         <v>37.4</v>
       </c>
       <c r="D164" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>86.02</v>
       </c>
       <c r="E164" s="16">
@@ -11825,7 +11858,7 @@
       <c r="AB164" s="14"/>
       <c r="AC164" s="14"/>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A165" s="14" t="s">
         <v>169</v>
       </c>
@@ -11836,7 +11869,7 @@
         <v>39.6</v>
       </c>
       <c r="D165" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>91.08</v>
       </c>
       <c r="E165" s="16"/>
@@ -11881,7 +11914,7 @@
       <c r="AB165" s="14"/>
       <c r="AC165" s="14"/>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A166" s="14"/>
       <c r="B166" s="25" t="s">
         <v>171</v>
@@ -11914,7 +11947,7 @@
       <c r="AB166" s="14"/>
       <c r="AC166" s="14"/>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A167" s="14" t="s">
         <v>543</v>
       </c>
@@ -11925,7 +11958,7 @@
         <v>32</v>
       </c>
       <c r="D167" s="16">
-        <f t="shared" ref="D167:D168" si="29">PRODUCT(C167,$D$1)</f>
+        <f t="shared" ref="D167:D168" si="30">PRODUCT(C167,$D$1)</f>
         <v>73.599999999999994</v>
       </c>
       <c r="E167" s="16"/>
@@ -11968,7 +12001,7 @@
       <c r="AB167" s="14"/>
       <c r="AC167" s="14"/>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A168" s="14" t="s">
         <v>172</v>
       </c>
@@ -11979,7 +12012,7 @@
         <v>35</v>
       </c>
       <c r="D168" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>80.5</v>
       </c>
       <c r="E168" s="16"/>
@@ -12022,7 +12055,7 @@
       <c r="AB168" s="14"/>
       <c r="AC168" s="14"/>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A169" s="14"/>
       <c r="B169" s="15"/>
       <c r="C169" s="54"/>
@@ -12053,7 +12086,7 @@
       <c r="AB169" s="14"/>
       <c r="AC169" s="14"/>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A170" s="14" t="s">
         <v>560</v>
       </c>
@@ -12064,7 +12097,7 @@
         <v>35.200000000000003</v>
       </c>
       <c r="D170" s="16">
-        <f t="shared" ref="D170:D172" si="30">PRODUCT(C170,$D$1)</f>
+        <f t="shared" ref="D170:D172" si="31">PRODUCT(C170,$D$1)</f>
         <v>80.959999999999994</v>
       </c>
       <c r="E170" s="16"/>
@@ -12109,7 +12142,7 @@
       <c r="AB170" s="14"/>
       <c r="AC170" s="14"/>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A171" s="14" t="s">
         <v>556</v>
       </c>
@@ -12120,7 +12153,7 @@
         <v>36.200000000000003</v>
       </c>
       <c r="D171" s="16">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>83.26</v>
       </c>
       <c r="E171" s="16"/>
@@ -12165,7 +12198,7 @@
       <c r="AB171" s="14"/>
       <c r="AC171" s="14"/>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A172" s="14" t="s">
         <v>557</v>
       </c>
@@ -12176,7 +12209,7 @@
         <v>37.4</v>
       </c>
       <c r="D172" s="16">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>86.02</v>
       </c>
       <c r="E172" s="16"/>
@@ -12221,7 +12254,7 @@
       <c r="AB172" s="14"/>
       <c r="AC172" s="14"/>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A173" s="14"/>
       <c r="B173" s="15"/>
       <c r="C173" s="54"/>
@@ -12252,7 +12285,7 @@
       <c r="AB173" s="14"/>
       <c r="AC173" s="14"/>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A174" s="14" t="s">
         <v>174</v>
       </c>
@@ -12263,7 +12296,7 @@
         <v>29.7</v>
       </c>
       <c r="D174" s="16">
-        <f t="shared" ref="D174:D182" si="31">PRODUCT(C174,$D$1)</f>
+        <f t="shared" ref="D174:D182" si="32">PRODUCT(C174,$D$1)</f>
         <v>68.309999999999988</v>
       </c>
       <c r="E174" s="16">
@@ -12310,7 +12343,7 @@
       <c r="AB174" s="14"/>
       <c r="AC174" s="14"/>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A175" s="14" t="s">
         <v>176</v>
       </c>
@@ -12321,7 +12354,7 @@
         <v>30.8</v>
       </c>
       <c r="D175" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>70.839999999999989</v>
       </c>
       <c r="E175" s="16">
@@ -12368,7 +12401,7 @@
       <c r="AB175" s="14"/>
       <c r="AC175" s="14"/>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A176" s="14" t="s">
         <v>178</v>
       </c>
@@ -12379,7 +12412,7 @@
         <v>31.9</v>
       </c>
       <c r="D176" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>73.36999999999999</v>
       </c>
       <c r="E176" s="16">
@@ -12426,7 +12459,7 @@
       <c r="AB176" s="14"/>
       <c r="AC176" s="14"/>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A177" s="14" t="s">
         <v>180</v>
       </c>
@@ -12437,7 +12470,7 @@
         <v>33</v>
       </c>
       <c r="D177" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>75.899999999999991</v>
       </c>
       <c r="E177" s="16">
@@ -12484,7 +12517,7 @@
       <c r="AB177" s="14"/>
       <c r="AC177" s="14"/>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A178" s="14" t="s">
         <v>182</v>
       </c>
@@ -12495,7 +12528,7 @@
         <v>34</v>
       </c>
       <c r="D178" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>78.199999999999989</v>
       </c>
       <c r="E178" s="16">
@@ -12542,7 +12575,7 @@
       <c r="AB178" s="14"/>
       <c r="AC178" s="14"/>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A179" s="14" t="s">
         <v>184</v>
       </c>
@@ -12553,7 +12586,7 @@
         <v>35</v>
       </c>
       <c r="D179" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>80.5</v>
       </c>
       <c r="E179" s="16">
@@ -12600,7 +12633,7 @@
       <c r="AB179" s="14"/>
       <c r="AC179" s="14"/>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A180" s="14" t="s">
         <v>554</v>
       </c>
@@ -12611,7 +12644,7 @@
         <v>36</v>
       </c>
       <c r="D180" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>82.8</v>
       </c>
       <c r="E180" s="16">
@@ -12658,7 +12691,7 @@
       <c r="AB180" s="14"/>
       <c r="AC180" s="14"/>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A181" s="14" t="s">
         <v>186</v>
       </c>
@@ -12669,7 +12702,7 @@
         <v>41.8</v>
       </c>
       <c r="D181" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>96.139999999999986</v>
       </c>
       <c r="E181" s="16">
@@ -12716,7 +12749,7 @@
       <c r="AB181" s="14"/>
       <c r="AC181" s="14"/>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A182" s="14" t="s">
         <v>188</v>
       </c>
@@ -12727,7 +12760,7 @@
         <v>44</v>
       </c>
       <c r="D182" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>101.19999999999999</v>
       </c>
       <c r="E182" s="16"/>
@@ -12772,7 +12805,7 @@
       <c r="AB182" s="14"/>
       <c r="AC182" s="14"/>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A183" s="14"/>
       <c r="B183" s="25" t="s">
         <v>190</v>
@@ -12805,7 +12838,7 @@
       <c r="AB183" s="14"/>
       <c r="AC183" s="14"/>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A184" s="14"/>
       <c r="C184" s="54"/>
       <c r="D184" s="16"/>
@@ -12835,7 +12868,7 @@
       <c r="AB184" s="14"/>
       <c r="AC184" s="14"/>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A185" s="14"/>
       <c r="B185" s="15"/>
       <c r="C185" s="54"/>
@@ -12866,7 +12899,7 @@
       <c r="AB185" s="14"/>
       <c r="AC185" s="14"/>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A186" s="14" t="s">
         <v>191</v>
       </c>
@@ -12877,7 +12910,7 @@
         <v>34.1</v>
       </c>
       <c r="D186" s="16">
-        <f t="shared" ref="D186:D189" si="32">PRODUCT(C186,$D$1)</f>
+        <f t="shared" ref="D186:D189" si="33">PRODUCT(C186,$D$1)</f>
         <v>78.429999999999993</v>
       </c>
       <c r="E186" s="16"/>
@@ -12922,7 +12955,7 @@
       <c r="AB186" s="14"/>
       <c r="AC186" s="14"/>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A187" s="14" t="s">
         <v>192</v>
       </c>
@@ -12933,7 +12966,7 @@
         <v>36.299999999999997</v>
       </c>
       <c r="D187" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>83.489999999999981</v>
       </c>
       <c r="E187" s="16"/>
@@ -12978,7 +13011,7 @@
       <c r="AB187" s="14"/>
       <c r="AC187" s="14"/>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A188" s="14" t="s">
         <v>193</v>
       </c>
@@ -12989,7 +13022,7 @@
         <v>37.4</v>
       </c>
       <c r="D188" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>86.02</v>
       </c>
       <c r="E188" s="16"/>
@@ -13034,7 +13067,7 @@
       <c r="AB188" s="14"/>
       <c r="AC188" s="14"/>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A189" s="14" t="s">
         <v>194</v>
       </c>
@@ -13045,7 +13078,7 @@
         <v>38.5</v>
       </c>
       <c r="D189" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>88.55</v>
       </c>
       <c r="E189" s="16"/>
@@ -13090,7 +13123,7 @@
       <c r="AB189" s="14"/>
       <c r="AC189" s="14"/>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A190" s="14"/>
       <c r="B190" s="25" t="s">
         <v>195</v>
@@ -13123,7 +13156,7 @@
       <c r="AB190" s="14"/>
       <c r="AC190" s="14"/>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A191" s="14"/>
       <c r="B191" s="15"/>
       <c r="C191" s="76"/>
@@ -13154,7 +13187,7 @@
       <c r="AB191" s="14"/>
       <c r="AC191" s="14"/>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A192" s="14" t="s">
         <v>196</v>
       </c>
@@ -13165,7 +13198,7 @@
         <v>45.1</v>
       </c>
       <c r="D192" s="16">
-        <f t="shared" ref="D192:D193" si="33">PRODUCT(C192,$D$1)</f>
+        <f t="shared" ref="D192:D193" si="34">PRODUCT(C192,$D$1)</f>
         <v>103.72999999999999</v>
       </c>
       <c r="E192" s="16"/>
@@ -13210,7 +13243,7 @@
       <c r="AB192" s="14"/>
       <c r="AC192" s="14"/>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A193" s="14" t="s">
         <v>197</v>
       </c>
@@ -13221,7 +13254,7 @@
         <v>47.3</v>
       </c>
       <c r="D193" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>108.78999999999999</v>
       </c>
       <c r="E193" s="16"/>
@@ -13272,7 +13305,7 @@
       <c r="AB193" s="14"/>
       <c r="AC193" s="14"/>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A194" s="14"/>
       <c r="B194" s="25" t="s">
         <v>154</v>
@@ -13305,7 +13338,7 @@
       <c r="AB194" s="14"/>
       <c r="AC194" s="14"/>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A195" s="14"/>
       <c r="B195" s="15"/>
       <c r="C195" s="54"/>
@@ -13336,7 +13369,7 @@
       <c r="AB195" s="14"/>
       <c r="AC195" s="14"/>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A196" s="14" t="s">
         <v>198</v>
       </c>
@@ -13347,7 +13380,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="D196" s="16">
-        <f t="shared" ref="D196:D199" si="34">PRODUCT(C196,$D$1)</f>
+        <f t="shared" ref="D196:D199" si="35">PRODUCT(C196,$D$1)</f>
         <v>10.119999999999999</v>
       </c>
       <c r="E196" s="16"/>
@@ -13380,7 +13413,7 @@
       <c r="AB196" s="14"/>
       <c r="AC196" s="14"/>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A197" s="14" t="s">
         <v>200</v>
       </c>
@@ -13391,7 +13424,7 @@
         <v>7.7</v>
       </c>
       <c r="D197" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.709999999999997</v>
       </c>
       <c r="E197" s="16"/>
@@ -13424,7 +13457,7 @@
       <c r="AB197" s="14"/>
       <c r="AC197" s="14"/>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A198" s="14" t="s">
         <v>202</v>
       </c>
@@ -13435,7 +13468,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="D198" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>10.119999999999999</v>
       </c>
       <c r="E198" s="16"/>
@@ -13468,7 +13501,7 @@
       <c r="AB198" s="14"/>
       <c r="AC198" s="14"/>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A199" s="14" t="s">
         <v>204</v>
       </c>
@@ -13479,7 +13512,7 @@
         <v>5.5</v>
       </c>
       <c r="D199" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>12.649999999999999</v>
       </c>
       <c r="E199" s="16"/>
@@ -13512,7 +13545,7 @@
       <c r="AB199" s="14"/>
       <c r="AC199" s="14"/>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A200" s="14"/>
       <c r="B200" s="15"/>
       <c r="C200" s="54"/>
@@ -13543,7 +13576,7 @@
       <c r="AB200" s="14"/>
       <c r="AC200" s="14"/>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A201" s="14"/>
       <c r="B201" s="15"/>
       <c r="C201" s="54"/>
@@ -13574,7 +13607,7 @@
       <c r="AB201" s="14"/>
       <c r="AC201" s="14"/>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A202" s="14" t="s">
         <v>206</v>
       </c>
@@ -13585,7 +13618,7 @@
         <v>11</v>
       </c>
       <c r="D202" s="16">
-        <f t="shared" ref="D202:D219" si="35">PRODUCT(C202,$D$1)</f>
+        <f t="shared" ref="D202:D219" si="36">PRODUCT(C202,$D$1)</f>
         <v>25.299999999999997</v>
       </c>
       <c r="E202" s="16"/>
@@ -13624,7 +13657,7 @@
       <c r="AB202" s="14"/>
       <c r="AC202" s="14"/>
     </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A203" s="14" t="s">
         <v>208</v>
       </c>
@@ -13635,7 +13668,7 @@
         <v>25.3</v>
       </c>
       <c r="D203" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>58.19</v>
       </c>
       <c r="E203" s="16"/>
@@ -13674,7 +13707,7 @@
       <c r="AB203" s="14"/>
       <c r="AC203" s="14"/>
     </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A204" s="14" t="s">
         <v>210</v>
       </c>
@@ -13685,7 +13718,7 @@
         <v>27.5</v>
       </c>
       <c r="D204" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>63.249999999999993</v>
       </c>
       <c r="E204" s="16"/>
@@ -13724,7 +13757,7 @@
       <c r="AB204" s="14"/>
       <c r="AC204" s="14"/>
     </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A205" s="14" t="s">
         <v>212</v>
       </c>
@@ -13735,7 +13768,7 @@
         <v>29.7</v>
       </c>
       <c r="D205" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>68.309999999999988</v>
       </c>
       <c r="E205" s="16"/>
@@ -13774,7 +13807,7 @@
       <c r="AB205" s="14"/>
       <c r="AC205" s="14"/>
     </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A206" s="14" t="s">
         <v>214</v>
       </c>
@@ -13785,7 +13818,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="D206" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>10.119999999999999</v>
       </c>
       <c r="E206" s="16"/>
@@ -13824,7 +13857,7 @@
       <c r="AB206" s="14"/>
       <c r="AC206" s="14"/>
     </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A207" s="14" t="s">
         <v>216</v>
       </c>
@@ -13835,7 +13868,7 @@
         <v>5.5</v>
       </c>
       <c r="D207" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.649999999999999</v>
       </c>
       <c r="E207" s="16"/>
@@ -13874,7 +13907,7 @@
       <c r="AB207" s="14"/>
       <c r="AC207" s="14"/>
     </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A208" s="14" t="s">
         <v>218</v>
       </c>
@@ -13885,7 +13918,7 @@
         <v>6.6</v>
       </c>
       <c r="D208" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15.179999999999998</v>
       </c>
       <c r="E208" s="16"/>
@@ -13924,7 +13957,7 @@
       <c r="AB208" s="14"/>
       <c r="AC208" s="14"/>
     </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A209" s="14" t="s">
         <v>220</v>
       </c>
@@ -13935,7 +13968,7 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="D209" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>20.009999999999998</v>
       </c>
       <c r="E209" s="16"/>
@@ -13974,7 +14007,7 @@
       <c r="AB209" s="14"/>
       <c r="AC209" s="14"/>
     </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A210" s="14" t="s">
         <v>222</v>
       </c>
@@ -13985,7 +14018,7 @@
         <v>1.65</v>
       </c>
       <c r="D210" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.7949999999999995</v>
       </c>
       <c r="E210" s="16"/>
@@ -14024,7 +14057,7 @@
       <c r="AB210" s="14"/>
       <c r="AC210" s="14"/>
     </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A211" s="14" t="s">
         <v>224</v>
       </c>
@@ -14035,7 +14068,7 @@
         <v>1.65</v>
       </c>
       <c r="D211" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.7949999999999995</v>
       </c>
       <c r="E211" s="16"/>
@@ -14074,7 +14107,7 @@
       <c r="AB211" s="14"/>
       <c r="AC211" s="14"/>
     </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A212" s="14" t="s">
         <v>226</v>
       </c>
@@ -14085,7 +14118,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D212" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5.0599999999999996</v>
       </c>
       <c r="E212" s="16"/>
@@ -14124,7 +14157,7 @@
       <c r="AB212" s="14"/>
       <c r="AC212" s="14"/>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A213" s="14" t="s">
         <v>228</v>
       </c>
@@ -14135,7 +14168,7 @@
         <v>2.75</v>
       </c>
       <c r="D213" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.3249999999999993</v>
       </c>
       <c r="E213" s="16"/>
@@ -14174,7 +14207,7 @@
       <c r="AB213" s="14"/>
       <c r="AC213" s="14"/>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A214" s="14" t="s">
         <v>230</v>
       </c>
@@ -14185,7 +14218,7 @@
         <v>2.75</v>
       </c>
       <c r="D214" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.3249999999999993</v>
       </c>
       <c r="E214" s="16"/>
@@ -14224,7 +14257,7 @@
       <c r="AB214" s="14"/>
       <c r="AC214" s="14"/>
     </row>
-    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A215" s="14" t="s">
         <v>232</v>
       </c>
@@ -14235,7 +14268,7 @@
         <v>3.3</v>
       </c>
       <c r="D215" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7.589999999999999</v>
       </c>
       <c r="E215" s="16"/>
@@ -14274,7 +14307,7 @@
       <c r="AB215" s="14"/>
       <c r="AC215" s="14"/>
     </row>
-    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A216" s="14" t="s">
         <v>234</v>
       </c>
@@ -14285,7 +14318,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="D216" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>10.119999999999999</v>
       </c>
       <c r="E216" s="16"/>
@@ -14324,7 +14357,7 @@
       <c r="AB216" s="14"/>
       <c r="AC216" s="14"/>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A217" s="14" t="s">
         <v>236</v>
       </c>
@@ -14335,7 +14368,7 @@
         <v>5.5</v>
       </c>
       <c r="D217" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.649999999999999</v>
       </c>
       <c r="E217" s="16"/>
@@ -14374,7 +14407,7 @@
       <c r="AB217" s="14"/>
       <c r="AC217" s="14"/>
     </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A218" s="14" t="s">
         <v>238</v>
       </c>
@@ -14385,7 +14418,7 @@
         <v>5.5</v>
       </c>
       <c r="D218" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.649999999999999</v>
       </c>
       <c r="E218" s="16"/>
@@ -14424,7 +14457,7 @@
       <c r="AB218" s="14"/>
       <c r="AC218" s="14"/>
     </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A219" s="14" t="s">
         <v>240</v>
       </c>
@@ -14435,7 +14468,7 @@
         <v>8.5</v>
       </c>
       <c r="D219" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>19.549999999999997</v>
       </c>
       <c r="E219" s="16"/>
@@ -14474,7 +14507,7 @@
       <c r="AB219" s="14"/>
       <c r="AC219" s="14"/>
     </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A220" s="14"/>
       <c r="B220" s="15"/>
       <c r="C220" s="54"/>
@@ -14505,7 +14538,7 @@
       <c r="AB220" s="14"/>
       <c r="AC220" s="14"/>
     </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A221" s="14" t="s">
         <v>242</v>
       </c>
@@ -14516,7 +14549,7 @@
         <v>9.25</v>
       </c>
       <c r="D221" s="16">
-        <f t="shared" ref="D221:D222" si="36">PRODUCT(C221,$D$1)</f>
+        <f t="shared" ref="D221:D222" si="37">PRODUCT(C221,$D$1)</f>
         <v>21.274999999999999</v>
       </c>
       <c r="E221" s="16"/>
@@ -14549,7 +14582,7 @@
       <c r="AB221" s="14"/>
       <c r="AC221" s="14"/>
     </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A222" s="14" t="s">
         <v>244</v>
       </c>
@@ -14560,7 +14593,7 @@
         <v>13.25</v>
       </c>
       <c r="D222" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>30.474999999999998</v>
       </c>
       <c r="E222" s="16"/>
@@ -14593,7 +14626,7 @@
       <c r="AB222" s="14"/>
       <c r="AC222" s="14"/>
     </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A223" s="14"/>
       <c r="B223" s="15"/>
       <c r="C223" s="54"/>
@@ -14624,7 +14657,7 @@
       <c r="AB223" s="14"/>
       <c r="AC223" s="14"/>
     </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A224" s="14" t="s">
         <v>541</v>
       </c>
@@ -14635,7 +14668,7 @@
         <v>30</v>
       </c>
       <c r="D224" s="16">
-        <f t="shared" ref="D224:D228" si="37">PRODUCT(C224,$D$1)</f>
+        <f t="shared" ref="D224:D228" si="38">PRODUCT(C224,$D$1)</f>
         <v>69</v>
       </c>
       <c r="E224" s="16"/>
@@ -14664,7 +14697,7 @@
       <c r="AB224" s="14"/>
       <c r="AC224" s="14"/>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A225" s="14" t="s">
         <v>542</v>
       </c>
@@ -14675,7 +14708,7 @@
         <v>40</v>
       </c>
       <c r="D225" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>92</v>
       </c>
       <c r="E225" s="16"/>
@@ -14704,7 +14737,7 @@
       <c r="AB225" s="14"/>
       <c r="AC225" s="14"/>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A226" s="14" t="s">
         <v>248</v>
       </c>
@@ -14715,7 +14748,7 @@
         <v>300</v>
       </c>
       <c r="D226" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>690</v>
       </c>
       <c r="E226" s="16"/>
@@ -14754,7 +14787,7 @@
       <c r="AB226" s="14"/>
       <c r="AC226" s="14"/>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A227" s="14" t="s">
         <v>250</v>
       </c>
@@ -14765,7 +14798,7 @@
         <v>600</v>
       </c>
       <c r="D227" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1380</v>
       </c>
       <c r="E227" s="16"/>
@@ -14804,7 +14837,7 @@
       <c r="AB227" s="14"/>
       <c r="AC227" s="14"/>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A228" s="14" t="s">
         <v>252</v>
       </c>
@@ -14815,7 +14848,7 @@
         <v>800</v>
       </c>
       <c r="D228" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1839.9999999999998</v>
       </c>
       <c r="E228" s="16"/>
@@ -14854,7 +14887,7 @@
       <c r="AB228" s="14"/>
       <c r="AC228" s="14"/>
     </row>
-    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A229" s="14"/>
       <c r="B229" s="15"/>
       <c r="C229" s="54"/>
@@ -14885,7 +14918,7 @@
       <c r="AB229" s="14"/>
       <c r="AC229" s="14"/>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A230" s="14" t="s">
         <v>254</v>
       </c>
@@ -14896,7 +14929,7 @@
         <v>2.5</v>
       </c>
       <c r="D230" s="16">
-        <f t="shared" ref="D230:D231" si="38">PRODUCT(C230,$D$1)</f>
+        <f t="shared" ref="D230:D231" si="39">PRODUCT(C230,$D$1)</f>
         <v>5.75</v>
       </c>
       <c r="E230" s="16"/>
@@ -14929,7 +14962,7 @@
       <c r="AB230" s="14"/>
       <c r="AC230" s="14"/>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A231" s="14" t="s">
         <v>255</v>
       </c>
@@ -14940,7 +14973,7 @@
         <v>4</v>
       </c>
       <c r="D231" s="16">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="E231" s="16"/>
@@ -14973,7 +15006,7 @@
       <c r="AB231" s="14"/>
       <c r="AC231" s="14"/>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A232" s="14"/>
       <c r="B232" s="15"/>
       <c r="C232" s="76"/>
@@ -15004,7 +15037,7 @@
       <c r="AB232" s="14"/>
       <c r="AC232" s="14"/>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A233" s="14" t="s">
         <v>256</v>
       </c>
@@ -15015,7 +15048,7 @@
         <v>42</v>
       </c>
       <c r="D233" s="16">
-        <f t="shared" ref="D233:D236" si="39">PRODUCT(C233,$D$1)</f>
+        <f t="shared" ref="D233:D236" si="40">PRODUCT(C233,$D$1)</f>
         <v>96.6</v>
       </c>
       <c r="E233" s="16"/>
@@ -15054,7 +15087,7 @@
       <c r="AB233" s="14"/>
       <c r="AC233" s="14"/>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A234" s="14" t="s">
         <v>258</v>
       </c>
@@ -15065,7 +15098,7 @@
         <v>42</v>
       </c>
       <c r="D234" s="16">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>96.6</v>
       </c>
       <c r="E234" s="16"/>
@@ -15104,7 +15137,7 @@
       <c r="AB234" s="14"/>
       <c r="AC234" s="14"/>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="14" t="s">
         <v>260</v>
       </c>
@@ -15115,7 +15148,7 @@
         <v>120</v>
       </c>
       <c r="D235" s="16">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>276</v>
       </c>
       <c r="E235" s="16"/>
@@ -15154,7 +15187,7 @@
       <c r="AB235" s="14"/>
       <c r="AC235" s="14"/>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A236" s="14" t="s">
         <v>262</v>
       </c>
@@ -15165,7 +15198,7 @@
         <v>150</v>
       </c>
       <c r="D236" s="16">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>345</v>
       </c>
       <c r="E236" s="16"/>
@@ -15204,7 +15237,7 @@
       <c r="AB236" s="14"/>
       <c r="AC236" s="14"/>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="14"/>
       <c r="B237" s="15"/>
       <c r="C237" s="76"/>
@@ -15235,7 +15268,7 @@
       <c r="AB237" s="14"/>
       <c r="AC237" s="14"/>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A238" s="14"/>
       <c r="B238" s="15"/>
       <c r="C238" s="76"/>
@@ -15266,7 +15299,7 @@
       <c r="AB238" s="14"/>
       <c r="AC238" s="14"/>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A239" s="14"/>
       <c r="B239" s="15"/>
       <c r="C239" s="76"/>
@@ -15297,7 +15330,7 @@
       <c r="AB239" s="14"/>
       <c r="AC239" s="14"/>
     </row>
-    <row r="240" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="78" t="s">
         <v>59</v>
       </c>
@@ -15368,7 +15401,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A241" s="14" t="s">
         <v>264</v>
       </c>
@@ -15379,7 +15412,7 @@
         <v>23.1</v>
       </c>
       <c r="D241" s="16">
-        <f t="shared" ref="D241:D242" si="40">PRODUCT(C241,$D$1)</f>
+        <f t="shared" ref="D241:D242" si="41">PRODUCT(C241,$D$1)</f>
         <v>53.13</v>
       </c>
       <c r="E241" s="16"/>
@@ -15424,7 +15457,7 @@
       <c r="AB241" s="14"/>
       <c r="AC241" s="14"/>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A242" s="14" t="s">
         <v>266</v>
       </c>
@@ -15435,7 +15468,7 @@
         <v>25.3</v>
       </c>
       <c r="D242" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>58.19</v>
       </c>
       <c r="E242" s="16"/>
@@ -15480,7 +15513,7 @@
       <c r="AB242" s="14"/>
       <c r="AC242" s="14"/>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A243" s="14"/>
       <c r="B243" s="15"/>
       <c r="C243" s="54"/>
@@ -15511,7 +15544,7 @@
       <c r="AB243" s="14"/>
       <c r="AC243" s="14"/>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A244" s="14"/>
       <c r="B244" s="15"/>
       <c r="C244" s="54"/>
@@ -15542,7 +15575,7 @@
       <c r="AB244" s="14"/>
       <c r="AC244" s="14"/>
     </row>
-    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A245" s="14" t="s">
         <v>268</v>
       </c>
@@ -15553,7 +15586,7 @@
         <v>61.5</v>
       </c>
       <c r="D245" s="16">
-        <f t="shared" ref="D245:D249" si="41">PRODUCT(C245,$D$1)</f>
+        <f t="shared" ref="D245:D249" si="42">PRODUCT(C245,$D$1)</f>
         <v>141.44999999999999</v>
       </c>
       <c r="E245" s="16"/>
@@ -15592,7 +15625,7 @@
       <c r="AB245" s="14"/>
       <c r="AC245" s="14"/>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A246" s="14" t="s">
         <v>270</v>
       </c>
@@ -15603,7 +15636,7 @@
         <v>62.6</v>
       </c>
       <c r="D246" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>143.97999999999999</v>
       </c>
       <c r="E246" s="16"/>
@@ -15642,7 +15675,7 @@
       <c r="AB246" s="14"/>
       <c r="AC246" s="14"/>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A247" s="14" t="s">
         <v>272</v>
       </c>
@@ -15653,7 +15686,7 @@
         <v>63.7</v>
       </c>
       <c r="D247" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>146.51</v>
       </c>
       <c r="E247" s="16"/>
@@ -15692,7 +15725,7 @@
       <c r="AB247" s="14"/>
       <c r="AC247" s="14"/>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A248" s="14" t="s">
         <v>274</v>
       </c>
@@ -15703,7 +15736,7 @@
         <v>64.8</v>
       </c>
       <c r="D248" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>149.04</v>
       </c>
       <c r="E248" s="16"/>
@@ -15742,7 +15775,7 @@
       <c r="AB248" s="14"/>
       <c r="AC248" s="14"/>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A249" s="14" t="s">
         <v>276</v>
       </c>
@@ -15753,7 +15786,7 @@
         <v>65.900000000000006</v>
       </c>
       <c r="D249" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>151.57</v>
       </c>
       <c r="E249" s="16"/>
@@ -15792,7 +15825,7 @@
       <c r="AB249" s="14"/>
       <c r="AC249" s="14"/>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A250" s="14"/>
       <c r="B250" s="25" t="s">
         <v>278</v>
@@ -15825,7 +15858,7 @@
       <c r="AB250" s="16"/>
       <c r="AC250" s="14"/>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A251" s="14"/>
       <c r="B251" s="15"/>
       <c r="C251" s="54"/>
@@ -15856,7 +15889,7 @@
       <c r="AB251" s="16"/>
       <c r="AC251" s="14"/>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A252" s="14"/>
       <c r="B252" s="15"/>
       <c r="C252" s="54"/>
@@ -15887,7 +15920,7 @@
       <c r="AB252" s="16"/>
       <c r="AC252" s="14"/>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A253" s="14" t="s">
         <v>279</v>
       </c>
@@ -15898,7 +15931,7 @@
         <v>76.8</v>
       </c>
       <c r="D253" s="16">
-        <f t="shared" ref="D253:D257" si="42">PRODUCT(C253,$D$1)</f>
+        <f t="shared" ref="D253:D257" si="43">PRODUCT(C253,$D$1)</f>
         <v>176.64</v>
       </c>
       <c r="E253" s="16"/>
@@ -15937,7 +15970,7 @@
       <c r="AB253" s="16"/>
       <c r="AC253" s="14"/>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A254" s="14" t="s">
         <v>281</v>
       </c>
@@ -15948,7 +15981,7 @@
         <v>77.900000000000006</v>
       </c>
       <c r="D254" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>179.17</v>
       </c>
       <c r="E254" s="16"/>
@@ -15987,7 +16020,7 @@
       <c r="AB254" s="16"/>
       <c r="AC254" s="14"/>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A255" s="14" t="s">
         <v>283</v>
       </c>
@@ -15998,7 +16031,7 @@
         <v>79</v>
       </c>
       <c r="D255" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>181.7</v>
       </c>
       <c r="E255" s="16"/>
@@ -16037,7 +16070,7 @@
       <c r="AB255" s="16"/>
       <c r="AC255" s="14"/>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A256" s="14" t="s">
         <v>285</v>
       </c>
@@ -16048,7 +16081,7 @@
         <v>80.099999999999994</v>
       </c>
       <c r="D256" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>184.22999999999996</v>
       </c>
       <c r="E256" s="16"/>
@@ -16087,7 +16120,7 @@
       <c r="AB256" s="16"/>
       <c r="AC256" s="14"/>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A257" s="14" t="s">
         <v>287</v>
       </c>
@@ -16098,7 +16131,7 @@
         <v>81.2</v>
       </c>
       <c r="D257" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>186.76</v>
       </c>
       <c r="E257" s="16"/>
@@ -16137,7 +16170,7 @@
       <c r="AB257" s="16"/>
       <c r="AC257" s="14"/>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A258" s="14"/>
       <c r="B258" s="25" t="s">
         <v>289</v>
@@ -16170,7 +16203,7 @@
       <c r="AB258" s="16"/>
       <c r="AC258" s="14"/>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A259" s="14"/>
       <c r="B259" s="15"/>
       <c r="C259" s="54"/>
@@ -16201,7 +16234,7 @@
       <c r="AB259" s="16"/>
       <c r="AC259" s="14"/>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A260" s="14"/>
       <c r="B260" s="15"/>
       <c r="C260" s="54"/>
@@ -16232,7 +16265,7 @@
       <c r="AB260" s="14"/>
       <c r="AC260" s="14"/>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A261" s="14" t="s">
         <v>290</v>
       </c>
@@ -16243,7 +16276,7 @@
         <v>79</v>
       </c>
       <c r="D261" s="16">
-        <f t="shared" ref="D261:D265" si="43">PRODUCT(C261,$D$1)</f>
+        <f t="shared" ref="D261:D265" si="44">PRODUCT(C261,$D$1)</f>
         <v>181.7</v>
       </c>
       <c r="E261" s="16"/>
@@ -16282,7 +16315,7 @@
       <c r="AB261" s="14"/>
       <c r="AC261" s="14"/>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A262" s="14" t="s">
         <v>292</v>
       </c>
@@ -16293,7 +16326,7 @@
         <v>80.099999999999994</v>
       </c>
       <c r="D262" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>184.22999999999996</v>
       </c>
       <c r="E262" s="16"/>
@@ -16332,7 +16365,7 @@
       <c r="AB262" s="14"/>
       <c r="AC262" s="14"/>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A263" s="14" t="s">
         <v>294</v>
       </c>
@@ -16343,7 +16376,7 @@
         <v>81.2</v>
       </c>
       <c r="D263" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>186.76</v>
       </c>
       <c r="E263" s="16"/>
@@ -16382,7 +16415,7 @@
       <c r="AB263" s="14"/>
       <c r="AC263" s="14"/>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A264" s="14" t="s">
         <v>296</v>
       </c>
@@ -16393,7 +16426,7 @@
         <v>82.3</v>
       </c>
       <c r="D264" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>189.29</v>
       </c>
       <c r="E264" s="16"/>
@@ -16432,7 +16465,7 @@
       <c r="AB264" s="14"/>
       <c r="AC264" s="14"/>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A265" s="14" t="s">
         <v>298</v>
       </c>
@@ -16443,7 +16476,7 @@
         <v>83.4</v>
       </c>
       <c r="D265" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>191.82</v>
       </c>
       <c r="E265" s="16"/>
@@ -16482,7 +16515,7 @@
       <c r="AB265" s="14"/>
       <c r="AC265" s="14"/>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A266" s="14"/>
       <c r="B266" s="25" t="s">
         <v>300</v>
@@ -16515,7 +16548,7 @@
       <c r="AB266" s="14"/>
       <c r="AC266" s="14"/>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A267" s="14"/>
       <c r="B267" s="15"/>
       <c r="C267" s="54"/>
@@ -16546,7 +16579,7 @@
       <c r="AB267" s="14"/>
       <c r="AC267" s="14"/>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A268" s="14" t="s">
         <v>490</v>
       </c>
@@ -16557,7 +16590,7 @@
         <v>37.4</v>
       </c>
       <c r="D268" s="16">
-        <f t="shared" ref="D268:D276" si="44">PRODUCT(C268,$D$1)</f>
+        <f t="shared" ref="D268:D276" si="45">PRODUCT(C268,$D$1)</f>
         <v>86.02</v>
       </c>
       <c r="E268" s="16"/>
@@ -16602,7 +16635,7 @@
       <c r="AB268" s="14"/>
       <c r="AC268" s="14"/>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A269" s="14" t="s">
         <v>491</v>
       </c>
@@ -16613,7 +16646,7 @@
         <v>38.5</v>
       </c>
       <c r="D269" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>88.55</v>
       </c>
       <c r="E269" s="16"/>
@@ -16658,7 +16691,7 @@
       <c r="AB269" s="14"/>
       <c r="AC269" s="14"/>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A270" s="14" t="s">
         <v>492</v>
       </c>
@@ -16669,7 +16702,7 @@
         <v>39.6</v>
       </c>
       <c r="D270" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>91.08</v>
       </c>
       <c r="E270" s="16"/>
@@ -16714,7 +16747,7 @@
       <c r="AB270" s="14"/>
       <c r="AC270" s="14"/>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A271" s="14" t="s">
         <v>484</v>
       </c>
@@ -16725,7 +16758,7 @@
         <v>41.8</v>
       </c>
       <c r="D271" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>96.139999999999986</v>
       </c>
       <c r="E271" s="16"/>
@@ -16770,7 +16803,7 @@
       <c r="AB271" s="14"/>
       <c r="AC271" s="14"/>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A272" s="14" t="s">
         <v>485</v>
       </c>
@@ -16781,7 +16814,7 @@
         <v>42.9</v>
       </c>
       <c r="D272" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>98.669999999999987</v>
       </c>
       <c r="E272" s="16"/>
@@ -16826,7 +16859,7 @@
       <c r="AB272" s="14"/>
       <c r="AC272" s="14"/>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A273" s="14" t="s">
         <v>486</v>
       </c>
@@ -16837,7 +16870,7 @@
         <v>47.3</v>
       </c>
       <c r="D273" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>108.78999999999999</v>
       </c>
       <c r="E273" s="16"/>
@@ -16882,7 +16915,7 @@
       <c r="AB273" s="14"/>
       <c r="AC273" s="14"/>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A274" s="14" t="s">
         <v>493</v>
       </c>
@@ -16893,7 +16926,7 @@
         <v>48.4</v>
       </c>
       <c r="D274" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>111.32</v>
       </c>
       <c r="E274" s="16"/>
@@ -16938,7 +16971,7 @@
       <c r="AB274" s="14"/>
       <c r="AC274" s="14"/>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A275" s="14" t="s">
         <v>487</v>
       </c>
@@ -16949,7 +16982,7 @@
         <v>49.5</v>
       </c>
       <c r="D275" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>113.85</v>
       </c>
       <c r="E275" s="16"/>
@@ -16994,7 +17027,7 @@
       <c r="AB275" s="14"/>
       <c r="AC275" s="14"/>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A276" s="14" t="s">
         <v>488</v>
       </c>
@@ -17005,7 +17038,7 @@
         <v>51.7</v>
       </c>
       <c r="D276" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>118.91</v>
       </c>
       <c r="E276" s="16"/>
@@ -17050,7 +17083,7 @@
       <c r="AB276" s="14"/>
       <c r="AC276" s="14"/>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A277" s="14"/>
       <c r="B277" s="15"/>
       <c r="C277" s="54"/>
@@ -17081,7 +17114,7 @@
       <c r="AB277" s="14"/>
       <c r="AC277" s="14"/>
     </row>
-    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A278" s="14" t="s">
         <v>301</v>
       </c>
@@ -17092,7 +17125,7 @@
         <v>30.8</v>
       </c>
       <c r="D278" s="16">
-        <f t="shared" ref="D278:D282" si="45">PRODUCT(C278,$D$1)</f>
+        <f t="shared" ref="D278:D282" si="46">PRODUCT(C278,$D$1)</f>
         <v>70.839999999999989</v>
       </c>
       <c r="E278" s="16"/>
@@ -17137,7 +17170,7 @@
       <c r="AB278" s="14"/>
       <c r="AC278" s="14"/>
     </row>
-    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A279" s="14" t="s">
         <v>303</v>
       </c>
@@ -17148,7 +17181,7 @@
         <v>31.9</v>
       </c>
       <c r="D279" s="16">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>73.36999999999999</v>
       </c>
       <c r="E279" s="16"/>
@@ -17193,7 +17226,7 @@
       <c r="AB279" s="14"/>
       <c r="AC279" s="14"/>
     </row>
-    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A280" s="14" t="s">
         <v>305</v>
       </c>
@@ -17204,7 +17237,7 @@
         <v>37.4</v>
       </c>
       <c r="D280" s="16">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>86.02</v>
       </c>
       <c r="E280" s="16"/>
@@ -17249,7 +17282,7 @@
       <c r="AB280" s="14"/>
       <c r="AC280" s="14"/>
     </row>
-    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A281" s="14" t="s">
         <v>307</v>
       </c>
@@ -17260,7 +17293,7 @@
         <v>40.700000000000003</v>
       </c>
       <c r="D281" s="16">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>93.61</v>
       </c>
       <c r="E281" s="16"/>
@@ -17305,7 +17338,7 @@
       <c r="AB281" s="14"/>
       <c r="AC281" s="14"/>
     </row>
-    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A282" s="14" t="s">
         <v>309</v>
       </c>
@@ -17316,7 +17349,7 @@
         <v>42.9</v>
       </c>
       <c r="D282" s="16">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>98.669999999999987</v>
       </c>
       <c r="E282" s="16"/>
@@ -17361,7 +17394,7 @@
       <c r="AB282" s="14"/>
       <c r="AC282" s="14"/>
     </row>
-    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A283" s="14"/>
       <c r="B283" s="25" t="s">
         <v>311</v>
@@ -17394,7 +17427,7 @@
       <c r="AB283" s="14"/>
       <c r="AC283" s="14"/>
     </row>
-    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A284" s="14"/>
       <c r="B284" s="15"/>
       <c r="C284" s="54"/>
@@ -17425,7 +17458,7 @@
       <c r="AB284" s="14"/>
       <c r="AC284" s="14"/>
     </row>
-    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A285" s="14"/>
       <c r="B285" s="15"/>
       <c r="C285" s="54"/>
@@ -17456,7 +17489,7 @@
       <c r="AB285" s="14"/>
       <c r="AC285" s="14"/>
     </row>
-    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A286" s="14" t="s">
         <v>312</v>
       </c>
@@ -17467,7 +17500,7 @@
         <v>29.7</v>
       </c>
       <c r="D286" s="16">
-        <f t="shared" ref="D286:D291" si="46">PRODUCT(C286,$D$1)</f>
+        <f t="shared" ref="D286:D291" si="47">PRODUCT(C286,$D$1)</f>
         <v>68.309999999999988</v>
       </c>
       <c r="E286" s="16"/>
@@ -17508,7 +17541,7 @@
       <c r="AB286" s="14"/>
       <c r="AC286" s="14"/>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A287" s="14" t="s">
         <v>314</v>
       </c>
@@ -17519,7 +17552,7 @@
         <v>30.8</v>
       </c>
       <c r="D287" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>70.839999999999989</v>
       </c>
       <c r="E287" s="16"/>
@@ -17560,7 +17593,7 @@
       <c r="AB287" s="14"/>
       <c r="AC287" s="14"/>
     </row>
-    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A288" s="14" t="s">
         <v>316</v>
       </c>
@@ -17571,7 +17604,7 @@
         <v>30.8</v>
       </c>
       <c r="D288" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>70.839999999999989</v>
       </c>
       <c r="E288" s="16"/>
@@ -17612,7 +17645,7 @@
       <c r="AB288" s="14"/>
       <c r="AC288" s="14"/>
     </row>
-    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A289" s="14" t="s">
         <v>318</v>
       </c>
@@ -17623,7 +17656,7 @@
         <v>33</v>
       </c>
       <c r="D289" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>75.899999999999991</v>
       </c>
       <c r="E289" s="16"/>
@@ -17664,7 +17697,7 @@
       <c r="AB289" s="14"/>
       <c r="AC289" s="14"/>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A290" s="14" t="s">
         <v>320</v>
       </c>
@@ -17675,7 +17708,7 @@
         <v>34.1</v>
       </c>
       <c r="D290" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>78.429999999999993</v>
       </c>
       <c r="E290" s="16"/>
@@ -17716,7 +17749,7 @@
       <c r="AB290" s="14"/>
       <c r="AC290" s="14"/>
     </row>
-    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A291" s="14" t="s">
         <v>322</v>
       </c>
@@ -17727,7 +17760,7 @@
         <v>35.200000000000003</v>
       </c>
       <c r="D291" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>80.959999999999994</v>
       </c>
       <c r="E291" s="16"/>
@@ -17768,7 +17801,7 @@
       <c r="AB291" s="14"/>
       <c r="AC291" s="14"/>
     </row>
-    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A292" s="14"/>
       <c r="B292" s="15"/>
       <c r="C292" s="54"/>
@@ -17799,7 +17832,7 @@
       <c r="AB292" s="14"/>
       <c r="AC292" s="14"/>
     </row>
-    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A293" s="14"/>
       <c r="B293" s="15"/>
       <c r="C293" s="54"/>
@@ -17830,7 +17863,7 @@
       <c r="AB293" s="14"/>
       <c r="AC293" s="14"/>
     </row>
-    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A294" s="14" t="s">
         <v>324</v>
       </c>
@@ -17841,7 +17874,7 @@
         <v>34.1</v>
       </c>
       <c r="D294" s="16">
-        <f t="shared" ref="D294:D297" si="47">PRODUCT(C294,$D$1)</f>
+        <f t="shared" ref="D294:D297" si="48">PRODUCT(C294,$D$1)</f>
         <v>78.429999999999993</v>
       </c>
       <c r="E294" s="16"/>
@@ -17872,7 +17905,7 @@
       <c r="AB294" s="14"/>
       <c r="AC294" s="14"/>
     </row>
-    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A295" s="14" t="s">
         <v>326</v>
       </c>
@@ -17883,7 +17916,7 @@
         <v>34.1</v>
       </c>
       <c r="D295" s="16">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>78.429999999999993</v>
       </c>
       <c r="E295" s="16"/>
@@ -17914,7 +17947,7 @@
       <c r="AB295" s="14"/>
       <c r="AC295" s="14"/>
     </row>
-    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A296" s="14" t="s">
         <v>328</v>
       </c>
@@ -17925,7 +17958,7 @@
         <v>51.7</v>
       </c>
       <c r="D296" s="16">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>118.91</v>
       </c>
       <c r="E296" s="16"/>
@@ -17956,7 +17989,7 @@
       <c r="AB296" s="14"/>
       <c r="AC296" s="14"/>
     </row>
-    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A297" s="14" t="s">
         <v>330</v>
       </c>
@@ -17967,7 +18000,7 @@
         <v>74.8</v>
       </c>
       <c r="D297" s="16">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>172.04</v>
       </c>
       <c r="E297" s="16"/>
@@ -17998,7 +18031,7 @@
       <c r="AB297" s="14"/>
       <c r="AC297" s="14"/>
     </row>
-    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A298" s="14"/>
       <c r="B298" s="15"/>
       <c r="C298" s="76"/>
@@ -18029,7 +18062,7 @@
       <c r="AB298" s="14"/>
       <c r="AC298" s="14"/>
     </row>
-    <row r="299" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="39"/>
       <c r="B299" s="82"/>
       <c r="C299" s="98"/>
@@ -18060,7 +18093,7 @@
       <c r="AB299" s="39"/>
       <c r="AC299" s="39"/>
     </row>
-    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B300" s="96" t="s">
         <v>567</v>
       </c>
@@ -18085,7 +18118,7 @@
       <c r="W300" s="2"/>
       <c r="X300" s="2"/>
     </row>
-    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B301" s="96" t="s">
         <v>568</v>
       </c>
@@ -18110,7 +18143,7 @@
       <c r="W301" s="2"/>
       <c r="X301" s="2"/>
     </row>
-    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B302" s="96" t="s">
         <v>569</v>
       </c>
@@ -18120,7 +18153,7 @@
         <v>17.48</v>
       </c>
     </row>
-    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B303" s="96" t="s">
         <v>570</v>
       </c>
@@ -18130,7 +18163,7 @@
         <v>22.28</v>
       </c>
     </row>
-    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B304" s="96" t="s">
         <v>571</v>
       </c>
@@ -18140,7 +18173,7 @@
         <v>27.18</v>
       </c>
     </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B305" s="96" t="s">
         <v>572</v>
       </c>
@@ -18150,13 +18183,13 @@
         <v>28.19</v>
       </c>
     </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B306" s="96"/>
       <c r="C306" s="103"/>
       <c r="D306" s="104"/>
       <c r="E306" s="102"/>
     </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B307" s="96" t="s">
         <v>573</v>
       </c>
@@ -18166,7 +18199,7 @@
         <v>10.96</v>
       </c>
     </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B308" s="96" t="s">
         <v>574</v>
       </c>
@@ -18176,7 +18209,7 @@
         <v>13.08</v>
       </c>
     </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B309" s="96" t="s">
         <v>575</v>
       </c>
@@ -18186,7 +18219,7 @@
         <v>15.21</v>
       </c>
     </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B310" s="96" t="s">
         <v>576</v>
       </c>
@@ -18196,7 +18229,7 @@
         <v>20.46</v>
       </c>
     </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B311" s="96" t="s">
         <v>577</v>
       </c>
@@ -18206,7 +18239,7 @@
         <v>24.74</v>
       </c>
     </row>
-    <row r="312" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B312" s="97" t="s">
         <v>578</v>
       </c>
@@ -18216,12 +18249,12 @@
         <v>25.91</v>
       </c>
     </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C313" s="103"/>
       <c r="D313" s="104"/>
       <c r="E313" s="104"/>
     </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B314" s="96" t="s">
         <v>601</v>
       </c>
@@ -18231,7 +18264,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B315" s="96" t="s">
         <v>607</v>
       </c>
@@ -18241,7 +18274,7 @@
         <v>10.42</v>
       </c>
     </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B316" s="96" t="s">
         <v>602</v>
       </c>
@@ -18251,7 +18284,7 @@
         <v>11.35</v>
       </c>
     </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B317" s="96" t="s">
         <v>603</v>
       </c>
@@ -18261,7 +18294,7 @@
         <v>12.66</v>
       </c>
     </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B318" s="96" t="s">
         <v>604</v>
       </c>
@@ -18271,7 +18304,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B319" s="96" t="s">
         <v>605</v>
       </c>
@@ -18281,7 +18314,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="320" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B320" s="97" t="s">
         <v>606</v>
       </c>
@@ -18291,12 +18324,12 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C321" s="103"/>
       <c r="D321" s="104"/>
       <c r="E321" s="104"/>
     </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B322" s="96" t="s">
         <v>615</v>
       </c>
@@ -18306,7 +18339,7 @@
         <v>17.010000000000002</v>
       </c>
     </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B323" s="96" t="s">
         <v>609</v>
       </c>
@@ -18316,7 +18349,7 @@
         <v>17.010000000000002</v>
       </c>
     </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B324" s="96" t="s">
         <v>610</v>
       </c>
@@ -18326,7 +18359,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B325" s="96" t="s">
         <v>611</v>
       </c>
@@ -18336,7 +18369,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B326" s="96" t="s">
         <v>612</v>
       </c>
@@ -18346,7 +18379,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B327" s="96" t="s">
         <v>613</v>
       </c>
@@ -18356,7 +18389,7 @@
         <v>39.020000000000003</v>
       </c>
     </row>
-    <row r="328" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B328" s="97" t="s">
         <v>614</v>
       </c>
@@ -18366,12 +18399,12 @@
         <v>39.020000000000003</v>
       </c>
     </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C329" s="103"/>
       <c r="D329" s="104"/>
       <c r="E329" s="105"/>
     </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B330" s="96" t="s">
         <v>622</v>
       </c>
@@ -18381,7 +18414,7 @@
         <v>13.98</v>
       </c>
     </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B331" s="96" t="s">
         <v>617</v>
       </c>
@@ -18391,7 +18424,7 @@
         <v>13.98</v>
       </c>
     </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B332" s="96" t="s">
         <v>618</v>
       </c>
@@ -18401,7 +18434,7 @@
         <v>16.47</v>
       </c>
     </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B333" s="96" t="s">
         <v>619</v>
       </c>
@@ -18411,7 +18444,7 @@
         <v>18.22</v>
       </c>
     </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B334" s="96" t="s">
         <v>616</v>
       </c>
@@ -18421,7 +18454,7 @@
         <v>24.24</v>
       </c>
     </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B335" s="96" t="s">
         <v>620</v>
       </c>
@@ -18431,7 +18464,7 @@
         <v>30.36</v>
       </c>
     </row>
-    <row r="336" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B336" s="97" t="s">
         <v>621</v>
       </c>
@@ -18453,24 +18486,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:AC81"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="60" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="65" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="65" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="65" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" style="6" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="60" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="65" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="65" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="65" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="6" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C2" s="8"/>
       <c r="D2" s="8">
         <v>2.2999999999999998</v>
@@ -18489,7 +18522,7 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
     </row>
-    <row r="3" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="110" t="s">
         <v>566</v>
       </c>
@@ -18504,7 +18537,7 @@
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
     </row>
-    <row r="4" spans="1:26" s="75" customFormat="1" ht="45.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" s="75" customFormat="1" ht="45.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="67" t="s">
         <v>59</v>
       </c>
@@ -18582,7 +18615,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
         <v>332</v>
       </c>
@@ -18657,7 +18690,7 @@
       <c r="Y5" s="43"/>
       <c r="Z5" s="43"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>334</v>
       </c>
@@ -18732,7 +18765,7 @@
       <c r="Y6" s="14"/>
       <c r="Z6" s="14"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>336</v>
       </c>
@@ -18807,7 +18840,7 @@
       <c r="Y7" s="14"/>
       <c r="Z7" s="14"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>338</v>
       </c>
@@ -18882,7 +18915,7 @@
       <c r="Y8" s="14"/>
       <c r="Z8" s="14"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>340</v>
       </c>
@@ -18957,7 +18990,7 @@
       <c r="Y9" s="14"/>
       <c r="Z9" s="14"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>342</v>
       </c>
@@ -19032,7 +19065,7 @@
       <c r="Y10" s="14"/>
       <c r="Z10" s="14"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="16"/>
@@ -19060,7 +19093,7 @@
       <c r="Y11" s="14"/>
       <c r="Z11" s="14"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
       <c r="C12" s="16"/>
@@ -19088,7 +19121,7 @@
       <c r="Y12" s="14"/>
       <c r="Z12" s="14"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>344</v>
       </c>
@@ -19163,7 +19196,7 @@
       <c r="Y13" s="14"/>
       <c r="Z13" s="14"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>346</v>
       </c>
@@ -19238,7 +19271,7 @@
       <c r="Y14" s="14"/>
       <c r="Z14" s="14"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>348</v>
       </c>
@@ -19313,7 +19346,7 @@
       <c r="Y15" s="14"/>
       <c r="Z15" s="14"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>350</v>
       </c>
@@ -19388,7 +19421,7 @@
       <c r="Y16" s="14"/>
       <c r="Z16" s="14"/>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="14"/>
       <c r="C17" s="16"/>
@@ -19416,7 +19449,7 @@
       <c r="Y17" s="14"/>
       <c r="Z17" s="14"/>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>352</v>
       </c>
@@ -19489,7 +19522,7 @@
       <c r="Y18" s="14"/>
       <c r="Z18" s="14"/>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
       <c r="B19" s="93" t="s">
         <v>354</v>
@@ -19519,7 +19552,7 @@
       <c r="Y19" s="14"/>
       <c r="Z19" s="14"/>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="93"/>
       <c r="C20" s="16"/>
@@ -19547,7 +19580,7 @@
       <c r="Y20" s="14"/>
       <c r="Z20" s="14"/>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>526</v>
       </c>
@@ -19590,7 +19623,7 @@
       <c r="Y21" s="14"/>
       <c r="Z21" s="14"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>531</v>
       </c>
@@ -19637,7 +19670,7 @@
       <c r="AA22" s="2"/>
       <c r="AC22" s="2"/>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>532</v>
       </c>
@@ -19684,7 +19717,7 @@
       <c r="AA23" s="2"/>
       <c r="AC23" s="2"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="14"/>
       <c r="B24" s="14"/>
       <c r="C24" s="26"/>
@@ -19712,7 +19745,7 @@
       <c r="Y24" s="14"/>
       <c r="Z24" s="14"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
       <c r="B25" s="14"/>
       <c r="C25" s="16"/>
@@ -19740,7 +19773,7 @@
       <c r="Y25" s="14"/>
       <c r="Z25" s="14"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>520</v>
       </c>
@@ -19787,7 +19820,7 @@
       <c r="Y26" s="14"/>
       <c r="Z26" s="14"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>518</v>
       </c>
@@ -19834,7 +19867,7 @@
       <c r="Y27" s="14"/>
       <c r="Z27" s="14"/>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>521</v>
       </c>
@@ -19881,7 +19914,7 @@
       <c r="Y28" s="14"/>
       <c r="Z28" s="14"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="94"/>
       <c r="C29" s="16"/>
@@ -19909,7 +19942,7 @@
       <c r="Y29" s="14"/>
       <c r="Z29" s="14"/>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>527</v>
       </c>
@@ -19950,7 +19983,7 @@
       <c r="Y30" s="14"/>
       <c r="Z30" s="14"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="16"/>
@@ -19978,7 +20011,7 @@
       <c r="Y31" s="14"/>
       <c r="Z31" s="14"/>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>355</v>
       </c>
@@ -20052,7 +20085,7 @@
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>357</v>
       </c>
@@ -20126,7 +20159,7 @@
       <c r="Y33" s="14"/>
       <c r="Z33" s="14"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>359</v>
       </c>
@@ -20200,7 +20233,7 @@
       <c r="Y34" s="14"/>
       <c r="Z34" s="14"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>361</v>
       </c>
@@ -20274,7 +20307,7 @@
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>363</v>
       </c>
@@ -20348,7 +20381,7 @@
       <c r="Y36" s="14"/>
       <c r="Z36" s="14"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="14"/>
       <c r="B37" s="93" t="s">
         <v>365</v>
@@ -20378,7 +20411,7 @@
       <c r="Y37" s="14"/>
       <c r="Z37" s="14"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="14"/>
       <c r="B38" s="94"/>
       <c r="C38" s="16"/>
@@ -20406,7 +20439,7 @@
       <c r="Y38" s="14"/>
       <c r="Z38" s="14"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>366</v>
       </c>
@@ -20476,7 +20509,7 @@
       <c r="Y39" s="14"/>
       <c r="Z39" s="14"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>368</v>
       </c>
@@ -20546,7 +20579,7 @@
       <c r="Y40" s="14"/>
       <c r="Z40" s="14"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>370</v>
       </c>
@@ -20616,7 +20649,7 @@
       <c r="Y41" s="14"/>
       <c r="Z41" s="14"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>372</v>
       </c>
@@ -20686,7 +20719,7 @@
       <c r="Y42" s="14"/>
       <c r="Z42" s="14"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>374</v>
       </c>
@@ -20756,7 +20789,7 @@
       <c r="Y43" s="14"/>
       <c r="Z43" s="14"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>376</v>
       </c>
@@ -20826,7 +20859,7 @@
       <c r="Y44" s="14"/>
       <c r="Z44" s="14"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="14"/>
       <c r="B45" s="94"/>
       <c r="C45" s="16"/>
@@ -20854,7 +20887,7 @@
       <c r="Y45" s="14"/>
       <c r="Z45" s="14"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>378</v>
       </c>
@@ -20924,7 +20957,7 @@
       <c r="Y46" s="14"/>
       <c r="Z46" s="14"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>380</v>
       </c>
@@ -20994,7 +21027,7 @@
       <c r="Y47" s="14"/>
       <c r="Z47" s="14"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>382</v>
       </c>
@@ -21064,7 +21097,7 @@
       <c r="Y48" s="14"/>
       <c r="Z48" s="14"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>384</v>
       </c>
@@ -21134,7 +21167,7 @@
       <c r="Y49" s="14"/>
       <c r="Z49" s="14"/>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>386</v>
       </c>
@@ -21203,7 +21236,7 @@
       <c r="Y50" s="14"/>
       <c r="Z50" s="14"/>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="14"/>
       <c r="B51" s="93" t="s">
         <v>388</v>
@@ -21233,7 +21266,7 @@
       <c r="Y51" s="14"/>
       <c r="Z51" s="14"/>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="14"/>
       <c r="B52" s="94"/>
       <c r="C52" s="16"/>
@@ -21261,7 +21294,7 @@
       <c r="Y52" s="14"/>
       <c r="Z52" s="14"/>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>389</v>
       </c>
@@ -21331,7 +21364,7 @@
       <c r="Y53" s="14"/>
       <c r="Z53" s="14"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>391</v>
       </c>
@@ -21401,7 +21434,7 @@
       <c r="Y54" s="14"/>
       <c r="Z54" s="14"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>393</v>
       </c>
@@ -21471,7 +21504,7 @@
       <c r="Y55" s="14"/>
       <c r="Z55" s="14"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>395</v>
       </c>
@@ -21541,7 +21574,7 @@
       <c r="Y56" s="14"/>
       <c r="Z56" s="14"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>397</v>
       </c>
@@ -21611,7 +21644,7 @@
       <c r="Y57" s="14"/>
       <c r="Z57" s="14"/>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
       <c r="B58" s="93" t="s">
         <v>388</v>
@@ -21641,7 +21674,7 @@
       <c r="Y58" s="14"/>
       <c r="Z58" s="14"/>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
       <c r="B59" s="94"/>
       <c r="C59" s="16"/>
@@ -21669,7 +21702,7 @@
       <c r="Y59" s="14"/>
       <c r="Z59" s="14"/>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>399</v>
       </c>
@@ -21739,7 +21772,7 @@
       <c r="Y60" s="14"/>
       <c r="Z60" s="14"/>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
         <v>401</v>
       </c>
@@ -21809,7 +21842,7 @@
       <c r="Y61" s="14"/>
       <c r="Z61" s="14"/>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>403</v>
       </c>
@@ -21879,7 +21912,7 @@
       <c r="Y62" s="14"/>
       <c r="Z62" s="14"/>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>405</v>
       </c>
@@ -21949,7 +21982,7 @@
       <c r="Y63" s="14"/>
       <c r="Z63" s="14"/>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>407</v>
       </c>
@@ -22019,7 +22052,7 @@
       <c r="Y64" s="14"/>
       <c r="Z64" s="14"/>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
       <c r="B65" s="93" t="s">
         <v>388</v>
@@ -22049,7 +22082,7 @@
       <c r="Y65" s="14"/>
       <c r="Z65" s="14"/>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="26"/>
@@ -22077,7 +22110,7 @@
       <c r="Y66" s="14"/>
       <c r="Z66" s="14"/>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="14"/>
       <c r="B67" s="94" t="s">
         <v>567</v>
@@ -22115,7 +22148,7 @@
       <c r="Y67" s="14"/>
       <c r="Z67" s="14"/>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="14"/>
       <c r="B68" s="94" t="s">
         <v>568</v>
@@ -22153,7 +22186,7 @@
       <c r="Y68" s="14"/>
       <c r="Z68" s="14"/>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="14"/>
       <c r="B69" s="94" t="s">
         <v>569</v>
@@ -22191,7 +22224,7 @@
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="14"/>
       <c r="B70" s="94" t="s">
         <v>570</v>
@@ -22229,7 +22262,7 @@
       <c r="Y70" s="14"/>
       <c r="Z70" s="14"/>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="14"/>
       <c r="B71" s="94" t="s">
         <v>571</v>
@@ -22267,7 +22300,7 @@
       <c r="Y71" s="14"/>
       <c r="Z71" s="14"/>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="14"/>
       <c r="B72" s="94" t="s">
         <v>572</v>
@@ -22305,7 +22338,7 @@
       <c r="Y72" s="14"/>
       <c r="Z72" s="14"/>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="14"/>
       <c r="B73" s="94"/>
       <c r="C73" s="26"/>
@@ -22333,7 +22366,7 @@
       <c r="Y73" s="14"/>
       <c r="Z73" s="14"/>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="14"/>
       <c r="B74" s="94" t="s">
         <v>573</v>
@@ -22371,7 +22404,7 @@
       <c r="Y74" s="14"/>
       <c r="Z74" s="14"/>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="14"/>
       <c r="B75" s="94" t="s">
         <v>574</v>
@@ -22409,7 +22442,7 @@
       <c r="Y75" s="14"/>
       <c r="Z75" s="14"/>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="14"/>
       <c r="B76" s="94" t="s">
         <v>575</v>
@@ -22447,7 +22480,7 @@
       <c r="Y76" s="14"/>
       <c r="Z76" s="14"/>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="14"/>
       <c r="B77" s="94" t="s">
         <v>576</v>
@@ -22485,7 +22518,7 @@
       <c r="Y77" s="14"/>
       <c r="Z77" s="14"/>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="14"/>
       <c r="B78" s="94" t="s">
         <v>577</v>
@@ -22523,7 +22556,7 @@
       <c r="Y78" s="14"/>
       <c r="Z78" s="14"/>
     </row>
-    <row r="79" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="39"/>
       <c r="B79" s="95" t="s">
         <v>578</v>
@@ -22561,7 +22594,7 @@
       <c r="Y79" s="39"/>
       <c r="Z79" s="39"/>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="E80" s="59"/>
       <c r="F80" s="12"/>
       <c r="G80" s="64"/>
@@ -22571,7 +22604,7 @@
       <c r="K80" s="64"/>
       <c r="L80" s="13"/>
     </row>
-    <row r="81" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E81" s="59"/>
       <c r="F81" s="12"/>
       <c r="G81" s="64"/>
@@ -22593,7 +22626,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
